--- a/CLOTHES_BY_NMCK_1910.xlsx
+++ b/CLOTHES_BY_NMCK_1910.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Одежда и СИЗ" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Одежда и СИЗ'!$A$3:$L$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Одежда и СИЗ'!$A$3:$L$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -57,12 +57,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -113,6 +128,24 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -131,16 +164,37 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -517,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -537,7 +591,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Одежда, спецодежда, СИЗ, форма — подача с 20.10.2026, без аукционов. От большей НМЦК к меньшей. Всего 36</t>
+          <t>Одежда, спецодежда, СИЗ, форма — подача с 20.10.2026, без аукционов. От большей НМЦК к меньшей. Всего 44</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -555,7 +609,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Себестоимость одежды: летний комплект 3 500 ₽, зимний 5 000 ₽; прочее — справочник цен 2026. Прибыль — после УСН 15% при ожидаемом снижении. Без НМЦК — внизу (коммерческие запросы КП).</t>
+          <t>Себестоимость одежды: летний комплект 3 500 ₽, зимний 5 000 ₽; прочее — справочник цен 2026. Прибыль — после УСН 15% при ожидаемом снижении. Без НМЦК — внизу (коммерческие запросы КП). Оранжевые строки — АУКЦИОНЫ (мы не участвуем, справочно).</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -637,136 +691,136 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="n">
+        <v>650000000</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>46324.41666666666</v>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>32616425940</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Поставка спецодежды, спецобуви и средств индивидуальной защиты</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>СПБ ГУП «Петербургский Метрополитен»</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>223-ФЗ · Аукцион в электронной форме</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>АУКЦИОН — не участвуем (справочно)</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>заявка: 13000000; контракт: 19500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="11" t="n">
         <v>200000000</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C5" s="12" t="n">
         <v>46317.45833333334</v>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>32616425363</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Поставка спецодежды и спецобуви для защиты от общепроизводственных загрязнений для нужд филиалов АО "Мособлэн…</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F5" s="14" t="inlineStr">
         <is>
           <t>АО «Московская Областная Энергосетевая Компания»</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>223-ФЗ · Закупка иного способа размещения</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H5" s="11" t="n">
         <v>133837274</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I5" s="15" t="n">
         <v>0.33081363</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J5" s="11" t="n">
         <v>34274206.97726028</v>
       </c>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t>Осторожно — жёсткие: рамочный; логотип; капитал и гарантии</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t>заявка: 1000000; контракт: 10000000; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="5" t="n">
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="11" t="n">
         <v>6990000</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C6" s="12" t="n">
         <v>46316.375</v>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>32616470223</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>Поставка средств индивидуальной защиты и спецодежды</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F6" s="14" t="inlineStr">
         <is>
           <t>Федеральное бюджетное учреждение Науки «Федеральный Научный…</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>223-ФЗ · Запрос котировок в электронной форме</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="9" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="17" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t>заявка: 69900; контракт: —; аванс: не указан</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>4169750</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>46325.5</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>B1510261835045</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Поставка форменной одежды для сотрудников службы безопасности АНО "Таврида.Арт"</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>АНО «Таврида.Арт»</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Коммерческие · Тендер</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>Посчитать: нужны позиции/цены</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
@@ -775,92 +829,92 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>1500000</v>
+        <v>5800000</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>46316.375</v>
+        <v>46323.375</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>32616453117</t>
+          <t>32616462000</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Спецодежда</t>
+          <t>Поставка термостойкой спецодежды для сотрудников</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>ГУП «Салаватводоканал»</t>
+          <t>АО «Рязанские Городские Распределительные Электрические Сет…</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>223-ФЗ · 223-ФЗ запрос предложений</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>681523</v>
-      </c>
-      <c r="I7" s="9" t="n">
-        <v>0.5456513333333333</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>539980.1497260274</v>
-      </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>ПОДАЁМ</t>
+          <t>223-ФЗ · Аукцион в электронной форме</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>АУКЦИОН — не участвуем (справочно)</t>
         </is>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>обеспечение: не указано</t>
+          <t>заявка: —; контракт: —</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>722838.15</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>46318.375</v>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>32616473060</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Право заключения договора на поставку средств защиты органов дыхания (СЭ)</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>ПАО «Россети Урал»</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>223-ФЗ · Запрос предложений в электронной форме</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>Посчитать: нужны позиции/цены</t>
-        </is>
-      </c>
-      <c r="L8" s="8" t="inlineStr">
-        <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
+      <c r="B8" s="19" t="n">
+        <v>4169750</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>46325.5</v>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>B1510261835045</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>Поставка форменной одежды для сотрудников службы безопасности АНО "Таврида.Арт"</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>АНО «Таврида.Арт»</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>Коммерческие · Тендер</t>
+        </is>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>2818752</v>
+      </c>
+      <c r="I8" s="23" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>689630</v>
+      </c>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>ОЦЕНКА: маржа ~32%, нужна спецификация</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
@@ -869,98 +923,92 @@
         <v>6</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>700000</v>
+        <v>2876920</v>
       </c>
       <c r="C9" s="6" t="n">
+        <v>46322.375</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>0114500000826002365</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Поставка зимнего обмундирования для ГКУ ПСС Республики Ингушетия.</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>ГКУ «Противопожарно-Спасательная Служба Республики Ингушети…</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ · Электронный аукцион</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="9" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>АУКЦИОН — не участвуем (справочно)</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>заявка: 28769.2; контракт: 10.00 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="C10" s="12" t="n">
         <v>46316.375</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>32616452870</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>32616453117</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Спецодежда</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>ГУП «Салаватводоканал» (2-й лот)</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>223-ФЗ · 223-ФЗ запрос котировок</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>558596</v>
-      </c>
-      <c r="I9" s="9" t="n">
-        <v>0.2020057142857142</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>40799.32</v>
-      </c>
-      <c r="K9" s="12" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>ГУП «Салаватводоканал»</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>223-ФЗ · 223-ФЗ запрос предложений</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>681523</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>0.5456513333333333</v>
+      </c>
+      <c r="J10" s="11" t="n">
+        <v>539980.1497260274</v>
+      </c>
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t>ПОДАЁМ</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="L10" s="14" t="inlineStr">
         <is>
           <t>обеспечение: не указано</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>671066</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>46317.20833333334</v>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>32616484297</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Поставка движимого имущества: костюм мужской «Горка 3» летний палатка для нужд МАУ ДО ДМЦ «Алый парус» города…</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>МАУ Дополнительного Образования Детский Морской Центр «Алый…</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>223-ФЗ · Закупка иного способа размещения</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>428582</v>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>0.3613415073927154</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>132987.0540252055</v>
-      </c>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>ПОДАЁМ</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
@@ -969,48 +1017,42 @@
         <v>8</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>498744.79</v>
+        <v>1122000</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>46317.20833333334</v>
+        <v>46321.375</v>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>0352500002526000085</t>
+          <t>0373100018726000059</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Поставка спецодежды и обуви (Реестровый номер 2026.066249)</t>
+          <t>Поставка ботинок с высокими берцами</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Бюджетное учреждение Омской обл. «Тевризское Дорожное Ремон…</t>
+          <t>ФГБОУ Высшего Образования «Академия Государственной Противо…</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электронной форме</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>384529.51</v>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>0.2290054598866085</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>40891.60656533697</v>
-      </c>
-      <c r="K11" s="12" t="inlineStr">
-        <is>
-          <t>ПОДАЁМ</t>
+          <t>44-ФЗ · Электронный аукцион</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>АУКЦИОН — не участвуем (справочно)</t>
         </is>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
+          <t>заявка: 11220; контракт: 10.00 %</t>
         </is>
       </c>
     </row>
@@ -1019,654 +1061,680 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="n">
+        <v>969134.64</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>46318.33333333334</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>0372100006526000016</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Поставка специальной одежды (термобельё мужское, куртка мужская демисезонная лётная)</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Федеральное казенное учреждение «Северо-Западный авиационны…</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>44-ФЗ · Электронный аукцион</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>АУКЦИОН — не участвуем (справочно)</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>заявка: —; контракт: 96913.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>722838.15</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>46318.375</v>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>32616473060</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Право заключения договора на поставку средств защиты органов дыхания (СЭ)</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>ПАО «Россети Урал»</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>223-ФЗ · Запрос предложений в электронной форме</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="17" t="inlineStr">
+        <is>
+          <t>Посчитать: нужны позиции/цены</t>
+        </is>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>700000</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>46316.375</v>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>32616452870</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Спецодежда</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>ГУП «Салаватводоканал» (2-й лот)</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>223-ФЗ · 223-ФЗ запрос котировок</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>558596</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>0.2020057142857142</v>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>40799.32</v>
+      </c>
+      <c r="K14" s="25" t="inlineStr">
+        <is>
+          <t>ПОДАЁМ</t>
+        </is>
+      </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>обеспечение: не указано</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>671066</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>46317.20833333334</v>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>32616484297</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Поставка движимого имущества: костюм мужской «Горка 3» летний палатка для нужд МАУ ДО ДМЦ «Алый парус» города…</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>МАУ Дополнительного Образования Детский Морской Центр «Алый…</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>223-ФЗ · Закупка иного способа размещения</t>
+        </is>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>428582</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>0.3613415073927154</v>
+      </c>
+      <c r="J15" s="11" t="n">
+        <v>132987.0540252055</v>
+      </c>
+      <c r="K15" s="25" t="inlineStr">
+        <is>
+          <t>ПОДАЁМ</t>
+        </is>
+      </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>498744.79</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>46317.20833333334</v>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>0352500002526000085</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Поставка спецодежды и обуви (Реестровый номер 2026.066249)</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>Бюджетное учреждение Омской обл. «Тевризское Дорожное Ремон…</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>44-ФЗ · Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>384529.51</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>0.2290054598866085</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>40891.60656533697</v>
+      </c>
+      <c r="K16" s="25" t="inlineStr">
+        <is>
+          <t>ПОДАЁМ</t>
+        </is>
+      </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="11" t="n">
         <v>498211.82</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C17" s="12" t="n">
         <v>46321.20833333334</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>0352500002526000089</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>Поставка спецодежды и обуви (Реестровый номер 2026.066998)</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>Бюджетное учреждение Омской обл. «Тевризское Дорожное Ремон…</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>44-ФЗ · Запрос котировок в электронной форме</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H17" s="11" t="n">
         <v>398347.84</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I17" s="15" t="n">
         <v>0.2004448228466358</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="J17" s="11" t="n">
         <v>28355.40972050412</v>
       </c>
-      <c r="K12" s="10" t="inlineStr">
+      <c r="K17" s="16" t="inlineStr">
         <is>
           <t>Осторожно — малая маржа</t>
         </is>
       </c>
-      <c r="L12" s="8" t="inlineStr">
+      <c r="L17" s="14" t="inlineStr">
         <is>
           <t>заявка: не требуется (в извещении не установлено) [пл.]; контракт: не требуется (в извещении не установлено) [пл.]; аванс: не указан — свер…</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="5" t="n">
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="11" t="n">
         <v>443486.33</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C18" s="12" t="n">
         <v>46317.33333333334</v>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>10762184</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Поставка спецодежды и средств индивидуальной защиты (СИЗ)</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>МАУ г. Новосибирска «Дирекция Городских Парков»</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="11" t="n"/>
+      <c r="K18" s="17" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L18" s="14" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="5" t="n">
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="11" t="n">
         <v>360300</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C19" s="12" t="n">
         <v>46316.54166666666</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>10771355</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>поставка одежды для обучающихся из числа ОВЗ, проживающих в общежитии</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>Государственное бюджетное Профессиональное Образовательное …</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="5" t="n"/>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="H19" s="11" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="17" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L19" s="14" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="5" t="n">
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="11" t="n">
         <v>269742</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C20" s="12" t="n">
         <v>46315.58333333334</v>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>588450</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>Закупка зимней спецодежды для дворников-разнорабочих.Обязательно предоставление сертификатов качества и образ…</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>ООО «Карсар»</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>Коммерческие · Конкурентный лист с переторжкой</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="5" t="n"/>
-      <c r="K15" s="11" t="inlineStr">
+      <c r="H20" s="11" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="11" t="n"/>
+      <c r="K20" s="17" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L15" s="8" t="inlineStr">
+      <c r="L20" s="14" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="5" t="n">
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="11" t="n">
         <v>203056.8</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C21" s="12" t="n">
         <v>46316.54166666666</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>588439</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>Закупка зимней одежды для управления главного механика.Обязательно предоставление сертификатов качества и обр…</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>ООО «Карсар»</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>Коммерческие · Конкурентный лист с переторжкой</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="5" t="n"/>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="17" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L16" s="8" t="inlineStr">
+      <c r="L21" s="14" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="5" t="n">
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="11" t="n">
         <v>159779</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C22" s="12" t="n">
         <v>46315</v>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>ИМЗ-2026-010566</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>Поставка спецодежды</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F22" s="14" t="inlineStr">
         <is>
           <t>Бюджетное Профессиональное Образовательное учреждение Чуваш…</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="11" t="inlineStr">
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="17" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L17" s="8" t="inlineStr">
+      <c r="L22" s="14" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="5" t="n">
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="11" t="n">
         <v>156229.45</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C23" s="12" t="n">
         <v>46315.25</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>32616454697</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>Поставка спецодежды для нужд бюджетного учреждения Омской области «Комплексный центр социального обслуживания…</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>Бюджетное учреждение Омской обл. «Комплексный Центр Социаль…</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>223-ФЗ · Запрос котировок в электронной форме</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="H23" s="11" t="n"/>
+      <c r="I23" s="15" t="n"/>
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="17" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="L23" s="14" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="5" t="n">
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="11" t="n">
         <v>120000</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C24" s="12" t="n">
         <v>46322.375</v>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>4067730</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>Запрос котировок в электронной форме № 31/ЗКТЭ-АО "РЖДстрой"/2026 на право заключения договора на поставку за…</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>АО «Рждстрой»</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>Коммерческие · Запрос котировок</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="11" t="n"/>
+      <c r="K24" s="17" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
+      <c r="L24" s="14" t="inlineStr">
         <is>
           <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="5" t="n">
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="11" t="n">
         <v>119400</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C25" s="12" t="n">
         <v>46316.54166666666</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>10771691</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>поставка одежды для обучающихся из числа ОВЗ, проживающих в общежитии</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>Государственное бюджетное Профессиональное Образовательное …</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="11" t="inlineStr">
+      <c r="H25" s="11" t="n"/>
+      <c r="I25" s="15" t="n"/>
+      <c r="J25" s="11" t="n"/>
+      <c r="K25" s="17" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="L25" s="14" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="5" t="n">
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="11" t="n">
         <v>91010</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C26" s="12" t="n">
         <v>46317.63680555556</v>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>10763937</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>Поставка мягкого инвентаря</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F26" s="14" t="inlineStr">
         <is>
           <t>Государственное бюджетное Дошкольное Образовательное учрежд…</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G26" s="14" t="inlineStr">
         <is>
           <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="11" t="inlineStr">
+      <c r="H26" s="11" t="n"/>
+      <c r="I26" s="15" t="n"/>
+      <c r="J26" s="11" t="n"/>
+      <c r="K26" s="17" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>12908</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>46316.59166666667</v>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>BP01597186</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>Приобретение средств индивидуальной защиты</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>МБУДО «Детская Школа Искусств Имени А.И.Островского» Городс…</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>Малые закупки · Малая закупка</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>Посчитать: нужны позиции/цены</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="6" t="n">
-        <v>46315.41666666666</v>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>4640791</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>RUNEV-11855, Аварийно-спасательное снаряжение - АО "Невинномысский Азот" - Ставропольский край</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>ОАО «Невинномысский Азот»</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>Коммерческие · Запрос предложений</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>КП — запросить спецификацию</t>
-        </is>
-      </c>
-      <c r="L23" s="8" t="inlineStr">
-        <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="6" t="n">
-        <v>46315.625</v>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>4638478</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>закупка спецодежды, СИЗ (поставка ноябрь 2026 - январь 2027 ежемесячно) для нужд ГК "УралМетКом" (ООО "УралМе…</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>ООО «Уралметком»</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>Коммерческие · Запрос предложений</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>КП — запросить спецификацию</t>
-        </is>
-      </c>
-      <c r="L24" s="8" t="inlineStr">
-        <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="6" t="n">
-        <v>46315.5</v>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>385-495</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>Спецодежда для персонала клининга и технической службы ГК Мэдокс</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>ООО «Мэдокс»</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>Коммерческие · Тендер</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="13" t="inlineStr">
-        <is>
-          <t>КП — запросить спецификацию</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="6" t="n">
-        <v>46316.99930555555</v>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>3506604</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>Поставка спецодежды и спецобуви для нужд Базы АО «В/О «Изотоп»</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>АО «Всерегиональное Объединение «Изотоп»</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>Коммерческие · Мониторинг цен</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="13" t="inlineStr">
-        <is>
-          <t>КП (сбор цен, без обязательств)</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
+      <c r="L26" s="14" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
@@ -1676,41 +1744,43 @@
       <c r="A27" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="5" t="n"/>
+      <c r="B27" s="5" t="n">
+        <v>85614.06</v>
+      </c>
       <c r="C27" s="6" t="n">
-        <v>46316.70833333334</v>
+        <v>46317.33333333334</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>4638381</t>
+          <t>0128200000126006161</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>«Бронежилеты и бронеодежда_КЧХК_10.2026»</t>
+          <t>Закупка жилетов разгрузочных для государственного бюджетного учреждения здравоохранения Владимирской области …</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Кчхк АО Охк Уралхим в г. К-Чепецке, ФЛ</t>
+          <t>ГБУЗ Владимирской обл. «Владимирская Областная Станция Скор…</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>Коммерческие · Процедура закупки</t>
+          <t>44-ФЗ · Электронный аукцион</t>
         </is>
       </c>
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="9" t="n"/>
       <c r="J27" s="5" t="n"/>
-      <c r="K27" s="13" t="inlineStr">
-        <is>
-          <t>КП — запросить спецификацию</t>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>АУКЦИОН — не участвуем (справочно)</t>
         </is>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
+          <t>заявка: —; контракт: 10.00 %</t>
         </is>
       </c>
     </row>
@@ -1718,41 +1788,43 @@
       <c r="A28" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="5" t="n"/>
+      <c r="B28" s="5" t="n">
+        <v>79800</v>
+      </c>
       <c r="C28" s="6" t="n">
-        <v>46316.375</v>
+        <v>46323.16666666666</v>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>384-590</t>
+          <t>0317300301926001566</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Закупка средств индивидуальной защиты (СИЗ рук, глаз), влагозащитной одежды и нательного белья</t>
+          <t>Поставка термобелья</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>ООО «Аэрозоль Новомосковск»</t>
+          <t>МКУ «Управление по делам гражданской обороны и чрезвычайным…</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>44-ФЗ · Электронный аукцион</t>
         </is>
       </c>
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="9" t="n"/>
       <c r="J28" s="5" t="n"/>
-      <c r="K28" s="13" t="inlineStr">
-        <is>
-          <t>КП — запросить спецификацию</t>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>АУКЦИОН — не участвуем (справочно)</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
+          <t>заявка: —; контракт: 30.00 %</t>
         </is>
       </c>
     </row>
@@ -1760,488 +1832,828 @@
       <c r="A29" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="5" t="n"/>
+      <c r="B29" s="5" t="n">
+        <v>20495</v>
+      </c>
       <c r="C29" s="6" t="n">
-        <v>46316.70416666667</v>
+        <v>46315.25</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>4642906</t>
+          <t>0260100000926000200</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Спецодежда, обувь и СИЗ</t>
+          <t>Поставка респираторов медицинских FFP3</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>ООО «Калинов Мост»</t>
+          <t>Федеральное бюджетное учреждение Центр Реабилитации Фонда П…</t>
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос предложений</t>
+          <t>44-ФЗ · Электронный аукцион</t>
         </is>
       </c>
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="9" t="n"/>
       <c r="J29" s="5" t="n"/>
-      <c r="K29" s="13" t="inlineStr">
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>АУКЦИОН — не участвуем (справочно)</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>заявка: —; контракт: 10.00 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>12908</v>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>46316.59166666667</v>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>BP01597186</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>Приобретение средств индивидуальной защиты</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>МБУДО «Детская Школа Искусств Имени А.И.Островского» Городс…</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>Малые закупки · Малая закупка</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="17" t="inlineStr">
+        <is>
+          <t>Посчитать: нужны позиции/цены</t>
+        </is>
+      </c>
+      <c r="L30" s="14" t="inlineStr">
+        <is>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="12" t="n">
+        <v>46315.41666666666</v>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>4640791</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>RUNEV-11855, Аварийно-спасательное снаряжение - АО "Невинномысский Азот" - Ставропольский край</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>ОАО «Невинномысский Азот»</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>Коммерческие · Запрос предложений</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="11" t="n"/>
+      <c r="K31" s="26" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr">
+      <c r="L31" s="14" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="6" t="n">
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="12" t="n">
+        <v>46315.625</v>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>4638478</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>закупка спецодежды, СИЗ (поставка ноябрь 2026 - январь 2027 ежемесячно) для нужд ГК "УралМетКом" (ООО "УралМе…</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>ООО «Уралметком»</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>Коммерческие · Запрос предложений</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="11" t="n"/>
+      <c r="K32" s="26" t="inlineStr">
+        <is>
+          <t>КП — запросить спецификацию</t>
+        </is>
+      </c>
+      <c r="L32" s="14" t="inlineStr">
+        <is>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="12" t="n">
+        <v>46315.5</v>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>385-495</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Спецодежда для персонала клининга и технической службы ГК Мэдокс</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>ООО «Мэдокс»</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>Коммерческие · Тендер</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="15" t="n"/>
+      <c r="J33" s="11" t="n"/>
+      <c r="K33" s="26" t="inlineStr">
+        <is>
+          <t>КП — запросить спецификацию</t>
+        </is>
+      </c>
+      <c r="L33" s="14" t="inlineStr">
+        <is>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="12" t="n">
+        <v>46316.99930555555</v>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>3506604</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Поставка спецодежды и спецобуви для нужд Базы АО «В/О «Изотоп»</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>АО «Всерегиональное Объединение «Изотоп»</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>Коммерческие · Мониторинг цен</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="n"/>
+      <c r="I34" s="15" t="n"/>
+      <c r="J34" s="11" t="n"/>
+      <c r="K34" s="26" t="inlineStr">
+        <is>
+          <t>КП (сбор цен, без обязательств)</t>
+        </is>
+      </c>
+      <c r="L34" s="14" t="inlineStr">
+        <is>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="12" t="n">
+        <v>46316.70833333334</v>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>4638381</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>«Бронежилеты и бронеодежда_КЧХК_10.2026»</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Кчхк АО Охк Уралхим в г. К-Чепецке, ФЛ</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>Коммерческие · Процедура закупки</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="15" t="n"/>
+      <c r="J35" s="11" t="n"/>
+      <c r="K35" s="26" t="inlineStr">
+        <is>
+          <t>КП — запросить спецификацию</t>
+        </is>
+      </c>
+      <c r="L35" s="14" t="inlineStr">
+        <is>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="12" t="n">
+        <v>46316.375</v>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>384-590</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>Закупка средств индивидуальной защиты (СИЗ рук, глаз), влагозащитной одежды и нательного белья</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>ООО «Аэрозоль Новомосковск»</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>Коммерческие · Тендер</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="n"/>
+      <c r="I36" s="15" t="n"/>
+      <c r="J36" s="11" t="n"/>
+      <c r="K36" s="26" t="inlineStr">
+        <is>
+          <t>КП — запросить спецификацию</t>
+        </is>
+      </c>
+      <c r="L36" s="14" t="inlineStr">
+        <is>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="12" t="n">
+        <v>46316.70416666667</v>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>4642906</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Спецодежда, обувь и СИЗ</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>ООО «Калинов Мост»</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>Коммерческие · Запрос предложений</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="n"/>
+      <c r="I37" s="15" t="n"/>
+      <c r="J37" s="11" t="n"/>
+      <c r="K37" s="26" t="inlineStr">
+        <is>
+          <t>КП — запросить спецификацию</t>
+        </is>
+      </c>
+      <c r="L37" s="14" t="inlineStr">
+        <is>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="10" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="12" t="n">
         <v>46316.29652777778</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>0573400000126006237</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t>Поставка специальной одежды, специальной обуви и других средств индивидуальной защиты для нужд Владивостокско…</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F38" s="14" t="inlineStr">
         <is>
           <t>ФГУП «Государственная Корпорация по Организации Воздушного …</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G38" s="14" t="inlineStr">
         <is>
           <t>44-ФЗ · Запрос цен</t>
         </is>
       </c>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="13" t="inlineStr">
+      <c r="H38" s="11" t="n"/>
+      <c r="I38" s="15" t="n"/>
+      <c r="J38" s="11" t="n"/>
+      <c r="K38" s="26" t="inlineStr">
         <is>
           <t>КП (сбор цен, без обязательств)</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr">
+      <c r="L38" s="14" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="40" customHeight="1">
-      <c r="A31" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="6" t="n">
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="10" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="12" t="n">
         <v>46317.45833333334</v>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>311-335</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>Закупка_ Консолидированная закупка СИЗ 2027 г._ просьба подать ваше предложение+ подготовить невозвратные обр…</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>АО «Прогресс»</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="13" t="inlineStr">
+      <c r="H39" s="11" t="n"/>
+      <c r="I39" s="15" t="n"/>
+      <c r="J39" s="11" t="n"/>
+      <c r="K39" s="26" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L31" s="8" t="inlineStr">
+      <c r="L39" s="14" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="6" t="n">
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="10" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="12" t="n">
         <v>46318.5</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>4644624</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>Респиратор фильтрующий Респираторный комплекс Алина-316 FFP3 R D ПДК50</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F40" s="14" t="inlineStr">
         <is>
           <t>ООО УК «Пмх»</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>Коммерческие · Запрос цен</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="13" t="inlineStr">
+      <c r="H40" s="11" t="n"/>
+      <c r="I40" s="15" t="n"/>
+      <c r="J40" s="11" t="n"/>
+      <c r="K40" s="26" t="inlineStr">
         <is>
           <t>КП (сбор цен, без обязательств)</t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
+      <c r="L40" s="14" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="40" customHeight="1">
-      <c r="A33" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="6" t="n">
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="10" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="12" t="n">
         <v>46318.45833333334</v>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>381-629</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>Закупка зимней спецодежды для ООО "Заречное". 2026г.</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>АО «Агрохолдинг «Просторы»</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="G41" s="14" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="13" t="inlineStr">
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="15" t="n"/>
+      <c r="J41" s="11" t="n"/>
+      <c r="K41" s="26" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L33" s="8" t="inlineStr">
+      <c r="L41" s="14" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="6" t="n">
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="10" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="12" t="n">
         <v>46318.58333333334</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>385-418</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E42" s="14" t="inlineStr">
         <is>
           <t>Закупка СИЗ г. Набережные Челны</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F42" s="14" t="inlineStr">
         <is>
           <t>ООО «Агк»</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G42" s="14" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="9" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="13" t="inlineStr">
+      <c r="H42" s="11" t="n"/>
+      <c r="I42" s="15" t="n"/>
+      <c r="J42" s="11" t="n"/>
+      <c r="K42" s="26" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L34" s="8" t="inlineStr">
+      <c r="L42" s="14" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="40" customHeight="1">
-      <c r="A35" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="6" t="n">
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="10" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="12" t="n">
         <v>46321.73611111111</v>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>386-076</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>Ботинки с высокими берцами - 4 000 пар</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F43" s="14" t="inlineStr">
         <is>
           <t>ООО «Союзспецодежда»</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="13" t="inlineStr">
+      <c r="H43" s="11" t="n"/>
+      <c r="I43" s="15" t="n"/>
+      <c r="J43" s="11" t="n"/>
+      <c r="K43" s="26" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L35" s="8" t="inlineStr">
+      <c r="L43" s="14" t="inlineStr">
         <is>
           <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="40" customHeight="1">
-      <c r="A36" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="6" t="n">
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="12" t="n">
         <v>46321.375</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>c5ec6e</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E44" s="14" t="inlineStr">
         <is>
           <t>спецодежда</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F44" s="14" t="inlineStr">
         <is>
           <t>АО «Зеленодольский Молочноперерабатывающий Комбинат»</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G44" s="14" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="13" t="inlineStr">
+      <c r="H44" s="11" t="n"/>
+      <c r="I44" s="15" t="n"/>
+      <c r="J44" s="11" t="n"/>
+      <c r="K44" s="26" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L36" s="8" t="inlineStr">
+      <c r="L44" s="14" t="inlineStr">
         <is>
           <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="40" customHeight="1">
-      <c r="A37" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="6" t="n">
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="12" t="n">
         <v>46321.5</v>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D45" s="13" t="inlineStr">
         <is>
           <t>4634447</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>Открытый запрос предложений по выбору ПУЛа поставщиков спецодежды для ГК Биннофарм Групп на 2026-2027 гг.</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>ООО «Биннофарм Групп»</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G45" s="14" t="inlineStr">
         <is>
           <t>Коммерческие · Запрос предложений</t>
         </is>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H45" s="11" t="n">
         <v>1209448</v>
       </c>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="13" t="inlineStr">
+      <c r="I45" s="15" t="n"/>
+      <c r="J45" s="11" t="n"/>
+      <c r="K45" s="26" t="inlineStr">
         <is>
           <t>КП ≈ 1 612 597 ₽ (без НМЦК)</t>
         </is>
       </c>
-      <c r="L37" s="8" t="inlineStr">
+      <c r="L45" s="14" t="inlineStr">
         <is>
           <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="40" customHeight="1">
-      <c r="A38" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="6" t="n">
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="12" t="n">
         <v>46321.41666666666</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>387-052</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E46" s="14" t="inlineStr">
         <is>
           <t>Закупка спец. одежды для предприятия под индивидуальное изготовление</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F46" s="14" t="inlineStr">
         <is>
           <t>АО «Евроцемент Груп»</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H38" s="5" t="n"/>
-      <c r="I38" s="9" t="n"/>
-      <c r="J38" s="5" t="n"/>
-      <c r="K38" s="13" t="inlineStr">
+      <c r="H46" s="11" t="n"/>
+      <c r="I46" s="15" t="n"/>
+      <c r="J46" s="11" t="n"/>
+      <c r="K46" s="26" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L38" s="8" t="inlineStr">
+      <c r="L46" s="14" t="inlineStr">
         <is>
           <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="40" customHeight="1">
-      <c r="A39" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="6" t="n">
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="12" t="n">
         <v>46330.5</v>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>386-334</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E47" s="14" t="inlineStr">
         <is>
           <t>СИЗ годовая потребность 2027</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F47" s="14" t="inlineStr">
         <is>
           <t>ООО «ТД «Доминант»</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H39" s="5" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="5" t="n"/>
-      <c r="K39" s="13" t="inlineStr">
+      <c r="H47" s="11" t="n"/>
+      <c r="I47" s="15" t="n"/>
+      <c r="J47" s="11" t="n"/>
+      <c r="K47" s="26" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L39" s="8" t="inlineStr">
+      <c r="L47" s="14" t="inlineStr">
         <is>
           <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="40" customHeight="1">
-      <c r="A40" s="14" t="inlineStr"/>
-      <c r="B40" s="15" t="n">
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="27" t="inlineStr"/>
+      <c r="B48" s="28" t="n">
         <v>217686522.34</v>
       </c>
-      <c r="C40" s="14" t="inlineStr"/>
-      <c r="D40" s="14" t="inlineStr"/>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>ИТОГО НМЦК</t>
-        </is>
-      </c>
-      <c r="F40" s="16" t="n"/>
-      <c r="G40" s="16" t="n"/>
-      <c r="H40" s="16" t="n"/>
-      <c r="I40" s="16" t="n"/>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="16" t="n"/>
+      <c r="C48" s="27" t="inlineStr"/>
+      <c r="D48" s="27" t="inlineStr"/>
+      <c r="E48" s="27" t="inlineStr">
+        <is>
+          <t>ИТОГО НМЦК без аукционов</t>
+        </is>
+      </c>
+      <c r="F48" s="29" t="n"/>
+      <c r="G48" s="29" t="n"/>
+      <c r="H48" s="29" t="n"/>
+      <c r="I48" s="29" t="n"/>
+      <c r="J48" s="29" t="n"/>
+      <c r="K48" s="29" t="n"/>
+      <c r="L48" s="29" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L39"/>
+  <autoFilter ref="A3:L47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/CLOTHES_BY_NMCK_1910.xlsx
+++ b/CLOTHES_BY_NMCK_1910.xlsx
@@ -18,12 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot; ₽&quot;"/>
-    <numFmt numFmtId="166" formatCode="DD.MM HH:MM"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0&quot; ₽&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +36,12 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -117,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -131,10 +135,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -149,10 +150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -173,10 +171,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,13 +192,13 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -576,7 +571,7 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
@@ -591,7 +586,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Одежда, спецодежда, СИЗ, форма — подача с 20.10.2026, без аукционов. От большей НМЦК к меньшей. Всего 44</t>
+          <t>Одежда, спецодежда, СИЗ, форма — подача с 20.10.2026 (аукционы — оранжевым, справочно). От большей НМЦК к меньшей. Всего 44</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -693,132 +688,138 @@
       <c r="B4" s="5" t="n">
         <v>650000000</v>
       </c>
-      <c r="C4" s="6" t="n">
-        <v>46324.41666666666</v>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>29.10.2026 10:00</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>32616425940</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Поставка спецодежды, спецобуви и средств индивидуальной защиты</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>СПБ ГУП «Петербургский Метрополитен»</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>223-ФЗ · Аукцион в электронной форме</t>
         </is>
       </c>
       <c r="H4" s="5" t="n"/>
-      <c r="I4" s="9" t="n"/>
+      <c r="I4" s="8" t="n"/>
       <c r="J4" s="5" t="n"/>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>АУКЦИОН — не участвуем (справочно)</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t>заявка: 13000000; контракт: 19500000</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="10" t="n">
         <v>200000000</v>
       </c>
-      <c r="C5" s="12" t="n">
-        <v>46317.45833333334</v>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>22.10.2026 11:00</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>32616425363</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Поставка спецодежды и спецобуви для защиты от общепроизводственных загрязнений для нужд филиалов АО "Мособлэн…</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>АО «Московская Областная Энергосетевая Компания»</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>223-ФЗ · Закупка иного способа размещения</t>
         </is>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="10" t="n">
         <v>133837274</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="13" t="n">
         <v>0.33081363</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="J5" s="10" t="n">
         <v>34274206.97726028</v>
       </c>
-      <c r="K5" s="16" t="inlineStr">
+      <c r="K5" s="14" t="inlineStr">
         <is>
           <t>Осторожно — жёсткие: рамочный; логотип; капитал и гарантии</t>
         </is>
       </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>заявка: 1000000; контракт: 10000000; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="10" t="n">
         <v>6990000</v>
       </c>
-      <c r="C6" s="12" t="n">
-        <v>46316.375</v>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>21.10.2026 09:00</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>32616470223</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>Поставка средств индивидуальной защиты и спецодежды</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t>Федеральное бюджетное учреждение Науки «Федеральный Научный…</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>223-ФЗ · Запрос котировок в электронной форме</t>
         </is>
       </c>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="11" t="n"/>
-      <c r="K6" s="17" t="inlineStr">
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="13" t="n"/>
+      <c r="J6" s="10" t="n"/>
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L6" s="14" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>заявка: 69900; контракт: —; аванс: не указан</t>
         </is>
@@ -831,88 +832,92 @@
       <c r="B7" s="5" t="n">
         <v>5800000</v>
       </c>
-      <c r="C7" s="6" t="n">
-        <v>46323.375</v>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>28.10.2026 09:00</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>32616462000</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Поставка термостойкой спецодежды для сотрудников</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>АО «Рязанские Городские Распределительные Электрические Сет…</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>223-ФЗ · Аукцион в электронной форме</t>
         </is>
       </c>
       <c r="H7" s="5" t="n"/>
-      <c r="I7" s="9" t="n"/>
+      <c r="I7" s="8" t="n"/>
       <c r="J7" s="5" t="n"/>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>АУКЦИОН — не участвуем (справочно)</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="17" t="n">
         <v>4169750</v>
       </c>
-      <c r="C8" s="20" t="n">
-        <v>46325.5</v>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>30.10.2026 12:00</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>B1510261835045</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Поставка форменной одежды для сотрудников службы безопасности АНО "Таврида.Арт"</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>АНО «Таврида.Арт»</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="17" t="n">
         <v>2818752</v>
       </c>
-      <c r="I8" s="23" t="n">
+      <c r="I8" s="20" t="n">
         <v>0.324</v>
       </c>
-      <c r="J8" s="19" t="n">
+      <c r="J8" s="17" t="n">
         <v>689630</v>
       </c>
-      <c r="K8" s="24" t="inlineStr">
+      <c r="K8" s="21" t="inlineStr">
         <is>
           <t>ОЦЕНКА: маржа ~32%, нужна спецификация</t>
         </is>
       </c>
-      <c r="L8" s="22" t="inlineStr">
+      <c r="L8" s="19" t="inlineStr">
         <is>
           <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
@@ -925,88 +930,92 @@
       <c r="B9" s="5" t="n">
         <v>2876920</v>
       </c>
-      <c r="C9" s="6" t="n">
-        <v>46322.375</v>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>27.10.2026 09:00</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>0114500000826002365</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Поставка зимнего обмундирования для ГКУ ПСС Республики Ингушетия.</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>ГКУ «Противопожарно-Спасательная Служба Республики Ингушети…</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>44-ФЗ · Электронный аукцион</t>
         </is>
       </c>
       <c r="H9" s="5" t="n"/>
-      <c r="I9" s="9" t="n"/>
+      <c r="I9" s="8" t="n"/>
       <c r="J9" s="5" t="n"/>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>АУКЦИОН — не участвуем (справочно)</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="L9" s="7" t="inlineStr">
         <is>
           <t>заявка: 28769.2; контракт: 10.00 %</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="C10" s="12" t="n">
-        <v>46316.375</v>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>21.10.2026 09:00</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>32616453117</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Спецодежда</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>ГУП «Салаватводоканал»</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>223-ФЗ · 223-ФЗ запрос предложений</t>
         </is>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="10" t="n">
         <v>681523</v>
       </c>
-      <c r="I10" s="15" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.5456513333333333</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J10" s="10" t="n">
         <v>539980.1497260274</v>
       </c>
-      <c r="K10" s="25" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>ПОДАЁМ</t>
         </is>
       </c>
-      <c r="L10" s="14" t="inlineStr">
+      <c r="L10" s="12" t="inlineStr">
         <is>
           <t>обеспечение: не указано</t>
         </is>
@@ -1019,38 +1028,40 @@
       <c r="B11" s="5" t="n">
         <v>1122000</v>
       </c>
-      <c r="C11" s="6" t="n">
-        <v>46321.375</v>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>26.10.2026 09:00</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>0373100018726000059</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Поставка ботинок с высокими берцами</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>ФГБОУ Высшего Образования «Академия Государственной Противо…</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>44-ФЗ · Электронный аукцион</t>
         </is>
       </c>
       <c r="H11" s="5" t="n"/>
-      <c r="I11" s="9" t="n"/>
+      <c r="I11" s="8" t="n"/>
       <c r="J11" s="5" t="n"/>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>АУКЦИОН — не участвуем (справочно)</t>
         </is>
       </c>
-      <c r="L11" s="8" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>заявка: 11220; контракт: 10.00 %</t>
         </is>
@@ -1063,678 +1074,708 @@
       <c r="B12" s="5" t="n">
         <v>969134.64</v>
       </c>
-      <c r="C12" s="6" t="n">
-        <v>46318.33333333334</v>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>23.10.2026 08:00</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>0372100006526000016</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Поставка специальной одежды (термобельё мужское, куртка мужская демисезонная лётная)</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Федеральное казенное учреждение «Северо-Западный авиационны…</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>44-ФЗ · Электронный аукцион</t>
         </is>
       </c>
       <c r="H12" s="5" t="n"/>
-      <c r="I12" s="9" t="n"/>
+      <c r="I12" s="8" t="n"/>
       <c r="J12" s="5" t="n"/>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>АУКЦИОН — не участвуем (справочно)</t>
         </is>
       </c>
-      <c r="L12" s="8" t="inlineStr">
+      <c r="L12" s="7" t="inlineStr">
         <is>
           <t>заявка: —; контракт: 96913.46</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="11" t="n">
+      <c r="B13" s="10" t="n">
         <v>722838.15</v>
       </c>
-      <c r="C13" s="12" t="n">
-        <v>46318.375</v>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>23.10.2026 09:00</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>32616473060</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Право заключения договора на поставку средств защиты органов дыхания (СЭ)</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>ПАО «Россети Урал»</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>223-ФЗ · Запрос предложений в электронной форме</t>
         </is>
       </c>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="17" t="inlineStr">
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="13" t="n"/>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="15" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L13" s="14" t="inlineStr">
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="10" t="n">
         <v>700000</v>
       </c>
-      <c r="C14" s="12" t="n">
-        <v>46316.375</v>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>21.10.2026 09:00</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>32616452870</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Спецодежда</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>ГУП «Салаватводоканал» (2-й лот)</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>223-ФЗ · 223-ФЗ запрос котировок</t>
         </is>
       </c>
-      <c r="H14" s="11" t="n">
+      <c r="H14" s="10" t="n">
         <v>558596</v>
       </c>
-      <c r="I14" s="15" t="n">
+      <c r="I14" s="13" t="n">
         <v>0.2020057142857142</v>
       </c>
-      <c r="J14" s="11" t="n">
+      <c r="J14" s="10" t="n">
         <v>40799.32</v>
       </c>
-      <c r="K14" s="25" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>ПОДАЁМ</t>
         </is>
       </c>
-      <c r="L14" s="14" t="inlineStr">
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t>обеспечение: не указано</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="11" t="n">
+      <c r="B15" s="10" t="n">
         <v>671066</v>
       </c>
-      <c r="C15" s="12" t="n">
-        <v>46317.20833333334</v>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>22.10.2026 05:00</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>32616484297</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Поставка движимого имущества: костюм мужской «Горка 3» летний палатка для нужд МАУ ДО ДМЦ «Алый парус» города…</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>МАУ Дополнительного Образования Детский Морской Центр «Алый…</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>223-ФЗ · Закупка иного способа размещения</t>
         </is>
       </c>
-      <c r="H15" s="11" t="n">
+      <c r="H15" s="10" t="n">
         <v>428582</v>
       </c>
-      <c r="I15" s="15" t="n">
+      <c r="I15" s="13" t="n">
         <v>0.3613415073927154</v>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="J15" s="10" t="n">
         <v>132987.0540252055</v>
       </c>
-      <c r="K15" s="25" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>ПОДАЁМ</t>
         </is>
       </c>
-      <c r="L15" s="14" t="inlineStr">
+      <c r="L15" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="10" t="n">
         <v>498744.79</v>
       </c>
-      <c r="C16" s="12" t="n">
-        <v>46317.20833333334</v>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>22.10.2026 05:00</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>0352500002526000085</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Поставка спецодежды и обуви (Реестровый номер 2026.066249)</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Бюджетное учреждение Омской обл. «Тевризское Дорожное Ремон…</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>44-ФЗ · Запрос котировок в электронной форме</t>
         </is>
       </c>
-      <c r="H16" s="11" t="n">
+      <c r="H16" s="10" t="n">
         <v>384529.51</v>
       </c>
-      <c r="I16" s="15" t="n">
+      <c r="I16" s="13" t="n">
         <v>0.2290054598866085</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" s="10" t="n">
         <v>40891.60656533697</v>
       </c>
-      <c r="K16" s="25" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>ПОДАЁМ</t>
         </is>
       </c>
-      <c r="L16" s="14" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="11" t="n">
+      <c r="B17" s="10" t="n">
         <v>498211.82</v>
       </c>
-      <c r="C17" s="12" t="n">
-        <v>46321.20833333334</v>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>26.10.2026 05:00</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>0352500002526000089</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Поставка спецодежды и обуви (Реестровый номер 2026.066998)</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Бюджетное учреждение Омской обл. «Тевризское Дорожное Ремон…</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>44-ФЗ · Запрос котировок в электронной форме</t>
         </is>
       </c>
-      <c r="H17" s="11" t="n">
+      <c r="H17" s="10" t="n">
         <v>398347.84</v>
       </c>
-      <c r="I17" s="15" t="n">
+      <c r="I17" s="13" t="n">
         <v>0.2004448228466358</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J17" s="10" t="n">
         <v>28355.40972050412</v>
       </c>
-      <c r="K17" s="16" t="inlineStr">
+      <c r="K17" s="14" t="inlineStr">
         <is>
           <t>Осторожно — малая маржа</t>
         </is>
       </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="L17" s="12" t="inlineStr">
         <is>
           <t>заявка: не требуется (в извещении не установлено) [пл.]; контракт: не требуется (в извещении не установлено) [пл.]; аванс: не указан — свер…</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="10" t="n">
         <v>443486.33</v>
       </c>
-      <c r="C18" s="12" t="n">
-        <v>46317.33333333334</v>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>22.10.2026 08:00</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>10762184</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Поставка спецодежды и средств индивидуальной защиты (СИЗ)</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>МАУ г. Новосибирска «Дирекция Городских Парков»</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
-      <c r="H18" s="11" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="11" t="n"/>
-      <c r="K18" s="17" t="inlineStr">
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="13" t="n"/>
+      <c r="J18" s="10" t="n"/>
+      <c r="K18" s="15" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L18" s="14" t="inlineStr">
+      <c r="L18" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="10" t="n">
+      <c r="A19" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" s="10" t="n">
         <v>360300</v>
       </c>
-      <c r="C19" s="12" t="n">
-        <v>46316.54166666666</v>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>21.10.2026 13:00</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>10771355</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>поставка одежды для обучающихся из числа ОВЗ, проживающих в общежитии</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Государственное бюджетное Профессиональное Образовательное …</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
-      <c r="H19" s="11" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="11" t="n"/>
-      <c r="K19" s="17" t="inlineStr">
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="13" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="15" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L19" s="14" t="inlineStr">
+      <c r="L19" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="11" t="n">
+      <c r="B20" s="10" t="n">
         <v>269742</v>
       </c>
-      <c r="C20" s="12" t="n">
-        <v>46315.58333333334</v>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>20.10.2026 14:00</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>588450</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Закупка зимней спецодежды для дворников-разнорабочих.Обязательно предоставление сертификатов качества и образ…</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>ООО «Карсар»</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Конкурентный лист с переторжкой</t>
         </is>
       </c>
-      <c r="H20" s="11" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="11" t="n"/>
-      <c r="K20" s="17" t="inlineStr">
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="13" t="n"/>
+      <c r="J20" s="10" t="n"/>
+      <c r="K20" s="15" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L20" s="14" t="inlineStr">
+      <c r="L20" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B21" s="10" t="n">
         <v>203056.8</v>
       </c>
-      <c r="C21" s="12" t="n">
-        <v>46316.54166666666</v>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>21.10.2026 13:00</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>588439</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Закупка зимней одежды для управления главного механика.Обязательно предоставление сертификатов качества и обр…</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>ООО «Карсар»</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Конкурентный лист с переторжкой</t>
         </is>
       </c>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="11" t="n"/>
-      <c r="K21" s="17" t="inlineStr">
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="13" t="n"/>
+      <c r="J21" s="10" t="n"/>
+      <c r="K21" s="15" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L21" s="14" t="inlineStr">
+      <c r="L21" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B22" s="10" t="n">
         <v>159779</v>
       </c>
-      <c r="C22" s="12" t="n">
-        <v>46315</v>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>20.10.2026 00:00</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>ИМЗ-2026-010566</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Поставка спецодежды</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>Бюджетное Профессиональное Образовательное учреждение Чуваш…</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
-      <c r="H22" s="11" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="11" t="n"/>
-      <c r="K22" s="17" t="inlineStr">
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="13" t="n"/>
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="15" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L22" s="14" t="inlineStr">
+      <c r="L22" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="11" t="n">
+      <c r="B23" s="10" t="n">
         <v>156229.45</v>
       </c>
-      <c r="C23" s="12" t="n">
-        <v>46315.25</v>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>20.10.2026 06:00</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>32616454697</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Поставка спецодежды для нужд бюджетного учреждения Омской области «Комплексный центр социального обслуживания…</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>Бюджетное учреждение Омской обл. «Комплексный Центр Социаль…</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>223-ФЗ · Запрос котировок в электронной форме</t>
         </is>
       </c>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="15" t="n"/>
-      <c r="J23" s="11" t="n"/>
-      <c r="K23" s="17" t="inlineStr">
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="13" t="n"/>
+      <c r="J23" s="10" t="n"/>
+      <c r="K23" s="15" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L23" s="14" t="inlineStr">
+      <c r="L23" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="10" t="n">
+      <c r="A24" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="11" t="n">
+      <c r="B24" s="10" t="n">
         <v>120000</v>
       </c>
-      <c r="C24" s="12" t="n">
-        <v>46322.375</v>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>27.10.2026 09:00</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>4067730</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Запрос котировок в электронной форме № 31/ЗКТЭ-АО "РЖДстрой"/2026 на право заключения договора на поставку за…</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>АО «Рждстрой»</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Запрос котировок</t>
         </is>
       </c>
-      <c r="H24" s="11" t="n"/>
-      <c r="I24" s="15" t="n"/>
-      <c r="J24" s="11" t="n"/>
-      <c r="K24" s="17" t="inlineStr">
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="13" t="n"/>
+      <c r="J24" s="10" t="n"/>
+      <c r="K24" s="15" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L24" s="14" t="inlineStr">
+      <c r="L24" s="12" t="inlineStr">
         <is>
           <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B25" s="10" t="n">
         <v>119400</v>
       </c>
-      <c r="C25" s="12" t="n">
-        <v>46316.54166666666</v>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>21.10.2026 13:00</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>10771691</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>поставка одежды для обучающихся из числа ОВЗ, проживающих в общежитии</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>Государственное бюджетное Профессиональное Образовательное …</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
-      <c r="H25" s="11" t="n"/>
-      <c r="I25" s="15" t="n"/>
-      <c r="J25" s="11" t="n"/>
-      <c r="K25" s="17" t="inlineStr">
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="13" t="n"/>
+      <c r="J25" s="10" t="n"/>
+      <c r="K25" s="15" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L25" s="14" t="inlineStr">
+      <c r="L25" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="10" t="n">
+      <c r="A26" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B26" s="10" t="n">
         <v>91010</v>
       </c>
-      <c r="C26" s="12" t="n">
-        <v>46317.63680555556</v>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>22.10.2026 15:17</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>10763937</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr">
         <is>
           <t>Поставка мягкого инвентаря</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>Государственное бюджетное Дошкольное Образовательное учрежд…</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
-      <c r="H26" s="11" t="n"/>
-      <c r="I26" s="15" t="n"/>
-      <c r="J26" s="11" t="n"/>
-      <c r="K26" s="17" t="inlineStr">
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="13" t="n"/>
+      <c r="J26" s="10" t="n"/>
+      <c r="K26" s="15" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L26" s="14" t="inlineStr">
+      <c r="L26" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
@@ -1747,38 +1788,40 @@
       <c r="B27" s="5" t="n">
         <v>85614.06</v>
       </c>
-      <c r="C27" s="6" t="n">
-        <v>46317.33333333334</v>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>22.10.2026 08:00</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>0128200000126006161</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Закупка жилетов разгрузочных для государственного бюджетного учреждения здравоохранения Владимирской области …</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>ГБУЗ Владимирской обл. «Владимирская Областная Станция Скор…</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>44-ФЗ · Электронный аукцион</t>
         </is>
       </c>
       <c r="H27" s="5" t="n"/>
-      <c r="I27" s="9" t="n"/>
+      <c r="I27" s="8" t="n"/>
       <c r="J27" s="5" t="n"/>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>АУКЦИОН — не участвуем (справочно)</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>заявка: —; контракт: 10.00 %</t>
         </is>
@@ -1791,38 +1834,40 @@
       <c r="B28" s="5" t="n">
         <v>79800</v>
       </c>
-      <c r="C28" s="6" t="n">
-        <v>46323.16666666666</v>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>28.10.2026 04:00</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>0317300301926001566</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>Поставка термобелья</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>МКУ «Управление по делам гражданской обороны и чрезвычайным…</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>44-ФЗ · Электронный аукцион</t>
         </is>
       </c>
       <c r="H28" s="5" t="n"/>
-      <c r="I28" s="9" t="n"/>
+      <c r="I28" s="8" t="n"/>
       <c r="J28" s="5" t="n"/>
-      <c r="K28" s="8" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>АУКЦИОН — не участвуем (справочно)</t>
         </is>
       </c>
-      <c r="L28" s="8" t="inlineStr">
+      <c r="L28" s="7" t="inlineStr">
         <is>
           <t>заявка: —; контракт: 30.00 %</t>
         </is>
@@ -1835,822 +1880,860 @@
       <c r="B29" s="5" t="n">
         <v>20495</v>
       </c>
-      <c r="C29" s="6" t="n">
-        <v>46315.25</v>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>20.10.2026 06:00</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>0260100000926000200</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>Поставка респираторов медицинских FFP3</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>Федеральное бюджетное учреждение Центр Реабилитации Фонда П…</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>44-ФЗ · Электронный аукцион</t>
         </is>
       </c>
       <c r="H29" s="5" t="n"/>
-      <c r="I29" s="9" t="n"/>
+      <c r="I29" s="8" t="n"/>
       <c r="J29" s="5" t="n"/>
-      <c r="K29" s="8" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>АУКЦИОН — не участвуем (справочно)</t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr">
+      <c r="L29" s="7" t="inlineStr">
         <is>
           <t>заявка: —; контракт: 10.00 %</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="10" t="n">
+      <c r="A30" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="11" t="n">
+      <c r="B30" s="10" t="n">
         <v>12908</v>
       </c>
-      <c r="C30" s="12" t="n">
-        <v>46316.59166666667</v>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>21.10.2026 14:12</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>BP01597186</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Приобретение средств индивидуальной защиты</t>
         </is>
       </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>МБУДО «Детская Школа Искусств Имени А.И.Островского» Городс…</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
-      <c r="H30" s="11" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="11" t="n"/>
-      <c r="K30" s="17" t="inlineStr">
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="13" t="n"/>
+      <c r="J30" s="10" t="n"/>
+      <c r="K30" s="15" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L30" s="14" t="inlineStr">
+      <c r="L30" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
-      <c r="A31" s="10" t="n">
+      <c r="A31" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="12" t="n">
-        <v>46315.41666666666</v>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>20.10.2026 10:00</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>4640791</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr">
         <is>
           <t>RUNEV-11855, Аварийно-спасательное снаряжение - АО "Невинномысский Азот" - Ставропольский край</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>ОАО «Невинномысский Азот»</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Запрос предложений</t>
         </is>
       </c>
-      <c r="H31" s="11" t="n"/>
-      <c r="I31" s="15" t="n"/>
-      <c r="J31" s="11" t="n"/>
-      <c r="K31" s="26" t="inlineStr">
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="13" t="n"/>
+      <c r="J31" s="10" t="n"/>
+      <c r="K31" s="23" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L31" s="14" t="inlineStr">
+      <c r="L31" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="10" t="n">
+      <c r="A32" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="12" t="n">
-        <v>46315.625</v>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>20.10.2026 15:00</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>4638478</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>закупка спецодежды, СИЗ (поставка ноябрь 2026 - январь 2027 ежемесячно) для нужд ГК "УралМетКом" (ООО "УралМе…</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>ООО «Уралметком»</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Запрос предложений</t>
         </is>
       </c>
-      <c r="H32" s="11" t="n"/>
-      <c r="I32" s="15" t="n"/>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="26" t="inlineStr">
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="13" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="23" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L32" s="14" t="inlineStr">
+      <c r="L32" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
-      <c r="A33" s="10" t="n">
+      <c r="A33" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="12" t="n">
-        <v>46315.5</v>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>20.10.2026 12:00</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>385-495</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Спецодежда для персонала клининга и технической службы ГК Мэдокс</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F33" s="12" t="inlineStr">
         <is>
           <t>ООО «Мэдокс»</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="15" t="n"/>
-      <c r="J33" s="11" t="n"/>
-      <c r="K33" s="26" t="inlineStr">
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="13" t="n"/>
+      <c r="J33" s="10" t="n"/>
+      <c r="K33" s="23" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L33" s="14" t="inlineStr">
+      <c r="L33" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="10" t="n">
+      <c r="A34" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="12" t="n">
-        <v>46316.99930555555</v>
-      </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>21.10.2026 23:59</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>3506604</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Поставка спецодежды и спецобуви для нужд Базы АО «В/О «Изотоп»</t>
         </is>
       </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>АО «Всерегиональное Объединение «Изотоп»</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Мониторинг цен</t>
         </is>
       </c>
-      <c r="H34" s="11" t="n"/>
-      <c r="I34" s="15" t="n"/>
-      <c r="J34" s="11" t="n"/>
-      <c r="K34" s="26" t="inlineStr">
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="13" t="n"/>
+      <c r="J34" s="10" t="n"/>
+      <c r="K34" s="23" t="inlineStr">
         <is>
           <t>КП (сбор цен, без обязательств)</t>
         </is>
       </c>
-      <c r="L34" s="14" t="inlineStr">
+      <c r="L34" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1">
-      <c r="A35" s="10" t="n">
+      <c r="A35" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="12" t="n">
-        <v>46316.70833333334</v>
-      </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>21.10.2026 17:00</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>4638381</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>«Бронежилеты и бронеодежда_КЧХК_10.2026»</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>Кчхк АО Охк Уралхим в г. К-Чепецке, ФЛ</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Процедура закупки</t>
         </is>
       </c>
-      <c r="H35" s="11" t="n"/>
-      <c r="I35" s="15" t="n"/>
-      <c r="J35" s="11" t="n"/>
-      <c r="K35" s="26" t="inlineStr">
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="13" t="n"/>
+      <c r="J35" s="10" t="n"/>
+      <c r="K35" s="23" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L35" s="14" t="inlineStr">
+      <c r="L35" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="36" ht="40" customHeight="1">
-      <c r="A36" s="10" t="n">
+      <c r="A36" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="12" t="n">
-        <v>46316.375</v>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>21.10.2026 09:00</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>384-590</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Закупка средств индивидуальной защиты (СИЗ рук, глаз), влагозащитной одежды и нательного белья</t>
         </is>
       </c>
-      <c r="F36" s="14" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>ООО «Аэрозоль Новомосковск»</t>
         </is>
       </c>
-      <c r="G36" s="14" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H36" s="11" t="n"/>
-      <c r="I36" s="15" t="n"/>
-      <c r="J36" s="11" t="n"/>
-      <c r="K36" s="26" t="inlineStr">
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="13" t="n"/>
+      <c r="J36" s="10" t="n"/>
+      <c r="K36" s="23" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L36" s="14" t="inlineStr">
+      <c r="L36" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1">
-      <c r="A37" s="10" t="n">
+      <c r="A37" s="9" t="n">
         <v>34</v>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="12" t="n">
-        <v>46316.70416666667</v>
-      </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>21.10.2026 16:54</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>4642906</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Спецодежда, обувь и СИЗ</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>ООО «Калинов Мост»</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Запрос предложений</t>
         </is>
       </c>
-      <c r="H37" s="11" t="n"/>
-      <c r="I37" s="15" t="n"/>
-      <c r="J37" s="11" t="n"/>
-      <c r="K37" s="26" t="inlineStr">
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="13" t="n"/>
+      <c r="J37" s="10" t="n"/>
+      <c r="K37" s="23" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L37" s="14" t="inlineStr">
+      <c r="L37" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1">
-      <c r="A38" s="10" t="n">
+      <c r="A38" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="12" t="n">
-        <v>46316.29652777778</v>
-      </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>21.10.2026 07:07</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>0573400000126006237</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Поставка специальной одежды, специальной обуви и других средств индивидуальной защиты для нужд Владивостокско…</t>
         </is>
       </c>
-      <c r="F38" s="14" t="inlineStr">
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>ФГУП «Государственная Корпорация по Организации Воздушного …</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>44-ФЗ · Запрос цен</t>
         </is>
       </c>
-      <c r="H38" s="11" t="n"/>
-      <c r="I38" s="15" t="n"/>
-      <c r="J38" s="11" t="n"/>
-      <c r="K38" s="26" t="inlineStr">
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="13" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="23" t="inlineStr">
         <is>
           <t>КП (сбор цен, без обязательств)</t>
         </is>
       </c>
-      <c r="L38" s="14" t="inlineStr">
+      <c r="L38" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1">
-      <c r="A39" s="10" t="n">
+      <c r="A39" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="12" t="n">
-        <v>46317.45833333334</v>
-      </c>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>22.10.2026 11:00</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>311-335</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr">
         <is>
           <t>Закупка_ Консолидированная закупка СИЗ 2027 г._ просьба подать ваше предложение+ подготовить невозвратные обр…</t>
         </is>
       </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>АО «Прогресс»</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
+      <c r="G39" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H39" s="11" t="n"/>
-      <c r="I39" s="15" t="n"/>
-      <c r="J39" s="11" t="n"/>
-      <c r="K39" s="26" t="inlineStr">
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="13" t="n"/>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="23" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L39" s="14" t="inlineStr">
+      <c r="L39" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1">
-      <c r="A40" s="10" t="n">
+      <c r="A40" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="12" t="n">
-        <v>46318.5</v>
-      </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>23.10.2026 12:00</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>4644624</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr">
         <is>
           <t>Респиратор фильтрующий Респираторный комплекс Алина-316 FFP3 R D ПДК50</t>
         </is>
       </c>
-      <c r="F40" s="14" t="inlineStr">
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>ООО УК «Пмх»</t>
         </is>
       </c>
-      <c r="G40" s="14" t="inlineStr">
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Запрос цен</t>
         </is>
       </c>
-      <c r="H40" s="11" t="n"/>
-      <c r="I40" s="15" t="n"/>
-      <c r="J40" s="11" t="n"/>
-      <c r="K40" s="26" t="inlineStr">
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="13" t="n"/>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="23" t="inlineStr">
         <is>
           <t>КП (сбор цен, без обязательств)</t>
         </is>
       </c>
-      <c r="L40" s="14" t="inlineStr">
+      <c r="L40" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
-      <c r="A41" s="10" t="n">
+      <c r="A41" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="12" t="n">
-        <v>46318.45833333334</v>
-      </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>23.10.2026 11:00</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>381-629</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
+      <c r="E41" s="12" t="inlineStr">
         <is>
           <t>Закупка зимней спецодежды для ООО "Заречное". 2026г.</t>
         </is>
       </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="F41" s="12" t="inlineStr">
         <is>
           <t>АО «Агрохолдинг «Просторы»</t>
         </is>
       </c>
-      <c r="G41" s="14" t="inlineStr">
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H41" s="11" t="n"/>
-      <c r="I41" s="15" t="n"/>
-      <c r="J41" s="11" t="n"/>
-      <c r="K41" s="26" t="inlineStr">
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="13" t="n"/>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="23" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L41" s="14" t="inlineStr">
+      <c r="L41" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
-      <c r="A42" s="10" t="n">
+      <c r="A42" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="12" t="n">
-        <v>46318.58333333334</v>
-      </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>23.10.2026 14:00</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>385-418</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Закупка СИЗ г. Набережные Челны</t>
         </is>
       </c>
-      <c r="F42" s="14" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>ООО «Агк»</t>
         </is>
       </c>
-      <c r="G42" s="14" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H42" s="11" t="n"/>
-      <c r="I42" s="15" t="n"/>
-      <c r="J42" s="11" t="n"/>
-      <c r="K42" s="26" t="inlineStr">
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="13" t="n"/>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="23" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L42" s="14" t="inlineStr">
+      <c r="L42" s="12" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
-      <c r="A43" s="10" t="n">
+      <c r="A43" s="9" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="12" t="n">
-        <v>46321.73611111111</v>
-      </c>
-      <c r="D43" s="13" t="inlineStr">
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>26.10.2026 17:40</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
         <is>
           <t>386-076</t>
         </is>
       </c>
-      <c r="E43" s="14" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>Ботинки с высокими берцами - 4 000 пар</t>
         </is>
       </c>
-      <c r="F43" s="14" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>ООО «Союзспецодежда»</t>
         </is>
       </c>
-      <c r="G43" s="14" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H43" s="11" t="n"/>
-      <c r="I43" s="15" t="n"/>
-      <c r="J43" s="11" t="n"/>
-      <c r="K43" s="26" t="inlineStr">
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="13" t="n"/>
+      <c r="J43" s="10" t="n"/>
+      <c r="K43" s="23" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L43" s="14" t="inlineStr">
+      <c r="L43" s="12" t="inlineStr">
         <is>
           <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
-      <c r="A44" s="10" t="n">
+      <c r="A44" s="9" t="n">
         <v>41</v>
       </c>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="12" t="n">
-        <v>46321.375</v>
-      </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>26.10.2026 09:00</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
         <is>
           <t>c5ec6e</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>спецодежда</t>
         </is>
       </c>
-      <c r="F44" s="14" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>АО «Зеленодольский Молочноперерабатывающий Комбинат»</t>
         </is>
       </c>
-      <c r="G44" s="14" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H44" s="11" t="n"/>
-      <c r="I44" s="15" t="n"/>
-      <c r="J44" s="11" t="n"/>
-      <c r="K44" s="26" t="inlineStr">
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="13" t="n"/>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="23" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L44" s="14" t="inlineStr">
+      <c r="L44" s="12" t="inlineStr">
         <is>
           <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
-      <c r="A45" s="10" t="n">
+      <c r="A45" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="12" t="n">
-        <v>46321.5</v>
-      </c>
-      <c r="D45" s="13" t="inlineStr">
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>26.10.2026 12:00</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
         <is>
           <t>4634447</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Открытый запрос предложений по выбору ПУЛа поставщиков спецодежды для ГК Биннофарм Групп на 2026-2027 гг.</t>
         </is>
       </c>
-      <c r="F45" s="14" t="inlineStr">
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>ООО «Биннофарм Групп»</t>
         </is>
       </c>
-      <c r="G45" s="14" t="inlineStr">
+      <c r="G45" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Запрос предложений</t>
         </is>
       </c>
-      <c r="H45" s="11" t="n">
+      <c r="H45" s="10" t="n">
         <v>1209448</v>
       </c>
-      <c r="I45" s="15" t="n"/>
-      <c r="J45" s="11" t="n"/>
-      <c r="K45" s="26" t="inlineStr">
+      <c r="I45" s="13" t="n"/>
+      <c r="J45" s="10" t="n"/>
+      <c r="K45" s="23" t="inlineStr">
         <is>
           <t>КП ≈ 1 612 597 ₽ (без НМЦК)</t>
         </is>
       </c>
-      <c r="L45" s="14" t="inlineStr">
+      <c r="L45" s="12" t="inlineStr">
         <is>
           <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
-      <c r="A46" s="10" t="n">
+      <c r="A46" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="12" t="n">
-        <v>46321.41666666666</v>
-      </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>26.10.2026 10:00</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>387-052</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr">
         <is>
           <t>Закупка спец. одежды для предприятия под индивидуальное изготовление</t>
         </is>
       </c>
-      <c r="F46" s="14" t="inlineStr">
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>АО «Евроцемент Груп»</t>
         </is>
       </c>
-      <c r="G46" s="14" t="inlineStr">
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H46" s="11" t="n"/>
-      <c r="I46" s="15" t="n"/>
-      <c r="J46" s="11" t="n"/>
-      <c r="K46" s="26" t="inlineStr">
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="13" t="n"/>
+      <c r="J46" s="10" t="n"/>
+      <c r="K46" s="23" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L46" s="14" t="inlineStr">
+      <c r="L46" s="12" t="inlineStr">
         <is>
           <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
-      <c r="A47" s="10" t="n">
+      <c r="A47" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="12" t="n">
-        <v>46330.5</v>
-      </c>
-      <c r="D47" s="13" t="inlineStr">
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>04.11.2026 12:00</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
         <is>
           <t>386-334</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>СИЗ годовая потребность 2027</t>
         </is>
       </c>
-      <c r="F47" s="14" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>ООО «ТД «Доминант»</t>
         </is>
       </c>
-      <c r="G47" s="14" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H47" s="11" t="n"/>
-      <c r="I47" s="15" t="n"/>
-      <c r="J47" s="11" t="n"/>
-      <c r="K47" s="26" t="inlineStr">
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="13" t="n"/>
+      <c r="J47" s="10" t="n"/>
+      <c r="K47" s="23" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
-      <c r="L47" s="14" t="inlineStr">
+      <c r="L47" s="12" t="inlineStr">
         <is>
           <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
-      <c r="A48" s="27" t="inlineStr"/>
-      <c r="B48" s="28" t="n">
+      <c r="A48" s="24" t="inlineStr"/>
+      <c r="B48" s="25" t="n">
         <v>217686522.34</v>
       </c>
-      <c r="C48" s="27" t="inlineStr"/>
-      <c r="D48" s="27" t="inlineStr"/>
-      <c r="E48" s="27" t="inlineStr">
+      <c r="C48" s="24" t="inlineStr"/>
+      <c r="D48" s="24" t="inlineStr"/>
+      <c r="E48" s="24" t="inlineStr">
         <is>
           <t>ИТОГО НМЦК без аукционов</t>
         </is>
       </c>
-      <c r="F48" s="29" t="n"/>
-      <c r="G48" s="29" t="n"/>
-      <c r="H48" s="29" t="n"/>
-      <c r="I48" s="29" t="n"/>
-      <c r="J48" s="29" t="n"/>
-      <c r="K48" s="29" t="n"/>
-      <c r="L48" s="29" t="n"/>
+      <c r="F48" s="26" t="n"/>
+      <c r="G48" s="26" t="n"/>
+      <c r="H48" s="26" t="n"/>
+      <c r="I48" s="26" t="n"/>
+      <c r="J48" s="26" t="n"/>
+      <c r="K48" s="26" t="n"/>
+      <c r="L48" s="26" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:L47"/>

--- a/CLOTHES_BY_NMCK_1910.xlsx
+++ b/CLOTHES_BY_NMCK_1910.xlsx
@@ -76,12 +76,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -168,6 +168,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -183,7 +186,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -784,286 +787,290 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="n">
-        <v>6990000</v>
+        <v>10800000</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>21.10.2026 09:00</t>
+          <t>26.10.2026 17:40</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>32616470223</t>
+          <t>386-076</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Поставка средств индивидуальной защиты и спецодежды</t>
+          <t>Ботинки с высокими берцами - 4 000 пар</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Федеральное бюджетное учреждение Науки «Федеральный Научный…</t>
+          <t>ООО «Союзспецодежда»</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>223-ФЗ · Запрос котировок в электронной форме</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="13" t="n"/>
+          <t>Коммерческие · Тендер</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>9600000</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>0.1111111111111112</v>
+      </c>
       <c r="J6" s="10" t="n"/>
       <c r="K6" s="15" t="inlineStr">
         <is>
+          <t>ОЦЕНКА КП ~10,8 млн: 4 000 пар × ~2 400 ₽ себес; маржа ~10%; снять спецификацию на Bidzaar</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>6990000</v>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>21.10.2026 09:00</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>32616470223</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Поставка средств индивидуальной защиты и спецодежды</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Федеральное бюджетное учреждение Науки «Федеральный Научный…</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>223-ФЗ · Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="13" t="n"/>
+      <c r="J7" s="10" t="n"/>
+      <c r="K7" s="16" t="inlineStr">
+        <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L7" s="12" t="inlineStr">
         <is>
           <t>заявка: 69900; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="n">
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="5" t="n">
         <v>5800000</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>28.10.2026 09:00</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>32616462000</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>Поставка термостойкой спецодежды для сотрудников</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>АО «Рязанские Городские Распределительные Электрические Сет…</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>223-ФЗ · Аукцион в электронной форме</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>АУКЦИОН — не участвуем (справочно)</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="L8" s="7" t="inlineStr">
         <is>
           <t>заявка: —; контракт: —</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="17" t="n">
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="18" t="n">
         <v>4169750</v>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>30.10.2026 12:00</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>B1510261835045</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>Поставка форменной одежды для сотрудников службы безопасности АНО "Таврида.Арт"</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>АНО «Таврида.Арт»</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>Коммерческие · Тендер</t>
         </is>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="H9" s="18" t="n">
         <v>2818752</v>
       </c>
-      <c r="I8" s="20" t="n">
+      <c r="I9" s="21" t="n">
         <v>0.324</v>
       </c>
-      <c r="J8" s="17" t="n">
+      <c r="J9" s="18" t="n">
         <v>689630</v>
       </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>ОЦЕНКА: маржа ~32%, нужна спецификация</t>
         </is>
       </c>
-      <c r="L8" s="19" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="5" t="n">
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="n">
         <v>2876920</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>27.10.2026 09:00</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>0114500000826002365</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Поставка зимнего обмундирования для ГКУ ПСС Республики Ингушетия.</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>ГКУ «Противопожарно-Спасательная Служба Республики Ингушети…</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>44-ФЗ · Электронный аукцион</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="8" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>АУКЦИОН — не участвуем (справочно)</t>
         </is>
       </c>
-      <c r="L9" s="7" t="inlineStr">
+      <c r="L10" s="7" t="inlineStr">
         <is>
           <t>заявка: 28769.2; контракт: 10.00 %</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="10" t="n">
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="10" t="n">
         <v>1500000</v>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>21.10.2026 09:00</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>32616453117</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Спецодежда</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>ГУП «Салаватводоканал»</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>223-ФЗ · 223-ФЗ запрос предложений</t>
         </is>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H11" s="10" t="n">
         <v>681523</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.5456513333333333</v>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="J11" s="10" t="n">
         <v>539980.1497260274</v>
       </c>
-      <c r="K10" s="22" t="inlineStr">
+      <c r="K11" s="23" t="inlineStr">
         <is>
           <t>ПОДАЁМ</t>
         </is>
       </c>
-      <c r="L10" s="12" t="inlineStr">
+      <c r="L11" s="12" t="inlineStr">
         <is>
           <t>обеспечение: не указано</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>1122000</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>26.10.2026 09:00</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>0373100018726000059</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Поставка ботинок с высокими берцами</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>ФГБОУ Высшего Образования «Академия Государственной Противо…</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>44-ФЗ · Электронный аукцион</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>АУКЦИОН — не участвуем (справочно)</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>заявка: 11220; контракт: 10.00 %</t>
         </is>
       </c>
     </row>
@@ -1072,26 +1079,26 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>969134.64</v>
+        <v>1122000</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>23.10.2026 08:00</t>
+          <t>26.10.2026 09:00</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>0372100006526000016</t>
+          <t>0373100018726000059</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Поставка специальной одежды (термобельё мужское, куртка мужская демисезонная лётная)</t>
+          <t>Поставка ботинок с высокими берцами</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Федеральное казенное учреждение «Северо-Западный авиационны…</t>
+          <t>ФГБОУ Высшего Образования «Академия Государственной Противо…</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -1109,53 +1116,53 @@
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
+          <t>заявка: 11220; контракт: 10.00 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>969134.64</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>23.10.2026 08:00</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>0372100006526000016</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Поставка специальной одежды (термобельё мужское, куртка мужская демисезонная лётная)</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Федеральное казенное учреждение «Северо-Западный авиационны…</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>44-ФЗ · Электронный аукцион</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>АУКЦИОН — не участвуем (справочно)</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
           <t>заявка: —; контракт: 96913.46</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>722838.15</v>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>23.10.2026 09:00</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>32616473060</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>Право заключения договора на поставку средств защиты органов дыхания (СЭ)</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>ПАО «Россети Урал»</t>
-        </is>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>223-ФЗ · Запрос предложений в электронной форме</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="13" t="n"/>
-      <c r="J13" s="10" t="n"/>
-      <c r="K13" s="15" t="inlineStr">
-        <is>
-          <t>Посчитать: нужны позиции/цены</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
@@ -1164,50 +1171,44 @@
         <v>11</v>
       </c>
       <c r="B14" s="10" t="n">
-        <v>700000</v>
+        <v>722838.15</v>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>21.10.2026 09:00</t>
+          <t>23.10.2026 09:00</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>32616452870</t>
+          <t>32616473060</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Спецодежда</t>
+          <t>Право заключения договора на поставку средств защиты органов дыхания (СЭ)</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>ГУП «Салаватводоканал» (2-й лот)</t>
+          <t>ПАО «Россети Урал»</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>223-ФЗ · 223-ФЗ запрос котировок</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>558596</v>
-      </c>
-      <c r="I14" s="13" t="n">
-        <v>0.2020057142857142</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>40799.32</v>
-      </c>
-      <c r="K14" s="22" t="inlineStr">
-        <is>
-          <t>ПОДАЁМ</t>
+          <t>223-ФЗ · Запрос предложений в электронной форме</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="13" t="n"/>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="16" t="inlineStr">
+        <is>
+          <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>обеспечение: не указано</t>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
@@ -1216,50 +1217,50 @@
         <v>12</v>
       </c>
       <c r="B15" s="10" t="n">
-        <v>671066</v>
+        <v>700000</v>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>22.10.2026 05:00</t>
+          <t>21.10.2026 09:00</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>32616484297</t>
+          <t>32616452870</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Поставка движимого имущества: костюм мужской «Горка 3» летний палатка для нужд МАУ ДО ДМЦ «Алый парус» города…</t>
+          <t>Спецодежда</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>МАУ Дополнительного Образования Детский Морской Центр «Алый…</t>
+          <t>ГУП «Салаватводоканал» (2-й лот)</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>223-ФЗ · Закупка иного способа размещения</t>
+          <t>223-ФЗ · 223-ФЗ запрос котировок</t>
         </is>
       </c>
       <c r="H15" s="10" t="n">
-        <v>428582</v>
+        <v>558596</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>0.3613415073927154</v>
+        <v>0.2020057142857142</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>132987.0540252055</v>
-      </c>
-      <c r="K15" s="22" t="inlineStr">
+        <v>40799.32</v>
+      </c>
+      <c r="K15" s="23" t="inlineStr">
         <is>
           <t>ПОДАЁМ</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
+          <t>обеспечение: не указано</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1269,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="10" t="n">
-        <v>498744.79</v>
+        <v>671066</v>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
@@ -1277,34 +1278,34 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>0352500002526000085</t>
+          <t>32616484297</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Поставка спецодежды и обуви (Реестровый номер 2026.066249)</t>
+          <t>Поставка движимого имущества: костюм мужской «Горка 3» летний палатка для нужд МАУ ДО ДМЦ «Алый парус» города…</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Бюджетное учреждение Омской обл. «Тевризское Дорожное Ремон…</t>
+          <t>МАУ Дополнительного Образования Детский Морской Центр «Алый…</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос котировок в электронной форме</t>
+          <t>223-ФЗ · Закупка иного способа размещения</t>
         </is>
       </c>
       <c r="H16" s="10" t="n">
-        <v>384529.51</v>
+        <v>428582</v>
       </c>
       <c r="I16" s="13" t="n">
-        <v>0.2290054598866085</v>
+        <v>0.3613415073927154</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>40891.60656533697</v>
-      </c>
-      <c r="K16" s="22" t="inlineStr">
+        <v>132987.0540252055</v>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
         <is>
           <t>ПОДАЁМ</t>
         </is>
@@ -1320,21 +1321,21 @@
         <v>14</v>
       </c>
       <c r="B17" s="10" t="n">
-        <v>498211.82</v>
+        <v>498744.79</v>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>26.10.2026 05:00</t>
+          <t>22.10.2026 05:00</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>0352500002526000089</t>
+          <t>0352500002526000085</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Поставка спецодежды и обуви (Реестровый номер 2026.066998)</t>
+          <t>Поставка спецодежды и обуви (Реестровый номер 2026.066249)</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -1348,22 +1349,22 @@
         </is>
       </c>
       <c r="H17" s="10" t="n">
-        <v>398347.84</v>
+        <v>384529.51</v>
       </c>
       <c r="I17" s="13" t="n">
-        <v>0.2004448228466358</v>
+        <v>0.2290054598866085</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>28355.40972050412</v>
-      </c>
-      <c r="K17" s="14" t="inlineStr">
-        <is>
-          <t>Осторожно — малая маржа</t>
+        <v>40891.60656533697</v>
+      </c>
+      <c r="K17" s="23" t="inlineStr">
+        <is>
+          <t>ПОДАЁМ</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>заявка: не требуется (в извещении не установлено) [пл.]; контракт: не требуется (в извещении не установлено) [пл.]; аванс: не указан — свер…</t>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
@@ -1372,44 +1373,50 @@
         <v>15</v>
       </c>
       <c r="B18" s="10" t="n">
-        <v>443486.33</v>
+        <v>498211.82</v>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>22.10.2026 08:00</t>
+          <t>26.10.2026 05:00</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>10762184</t>
+          <t>0352500002526000089</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Поставка спецодежды и средств индивидуальной защиты (СИЗ)</t>
+          <t>Поставка спецодежды и обуви (Реестровый номер 2026.066998)</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>МАУ г. Новосибирска «Дирекция Городских Парков»</t>
+          <t>Бюджетное учреждение Омской обл. «Тевризское Дорожное Ремон…</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Малые закупки · Малая закупка</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="13" t="n"/>
-      <c r="J18" s="10" t="n"/>
-      <c r="K18" s="15" t="inlineStr">
-        <is>
-          <t>Посчитать: нужны позиции/цены</t>
+          <t>44-ФЗ · Запрос котировок в электронной форме</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>398347.84</v>
+      </c>
+      <c r="I18" s="13" t="n">
+        <v>0.2004448228466358</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>28355.40972050412</v>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>Осторожно — малая маржа</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
+          <t>заявка: не требуется (в извещении не установлено) [пл.]; контракт: не требуется (в извещении не установлено) [пл.]; аванс: не указан — свер…</t>
         </is>
       </c>
     </row>
@@ -1418,26 +1425,26 @@
         <v>16</v>
       </c>
       <c r="B19" s="10" t="n">
-        <v>360300</v>
+        <v>443486.33</v>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>21.10.2026 13:00</t>
+          <t>22.10.2026 08:00</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>10771355</t>
+          <t>10762184</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>поставка одежды для обучающихся из числа ОВЗ, проживающих в общежитии</t>
+          <t>Поставка спецодежды и средств индивидуальной защиты (СИЗ)</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Государственное бюджетное Профессиональное Образовательное …</t>
+          <t>МАУ г. Новосибирска «Дирекция Городских Парков»</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -1448,7 +1455,7 @@
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="13" t="n"/>
       <c r="J19" s="10" t="n"/>
-      <c r="K19" s="15" t="inlineStr">
+      <c r="K19" s="16" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
@@ -1464,37 +1471,37 @@
         <v>17</v>
       </c>
       <c r="B20" s="10" t="n">
-        <v>269742</v>
+        <v>360300</v>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>20.10.2026 14:00</t>
+          <t>21.10.2026 13:00</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>588450</t>
+          <t>10771355</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Закупка зимней спецодежды для дворников-разнорабочих.Обязательно предоставление сертификатов качества и образ…</t>
+          <t>поставка одежды для обучающихся из числа ОВЗ, проживающих в общежитии</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>ООО «Карсар»</t>
+          <t>Государственное бюджетное Профессиональное Образовательное …</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Коммерческие · Конкурентный лист с переторжкой</t>
+          <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
       <c r="H20" s="10" t="n"/>
       <c r="I20" s="13" t="n"/>
       <c r="J20" s="10" t="n"/>
-      <c r="K20" s="15" t="inlineStr">
+      <c r="K20" s="16" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
@@ -1510,21 +1517,21 @@
         <v>18</v>
       </c>
       <c r="B21" s="10" t="n">
-        <v>203056.8</v>
+        <v>269742</v>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>21.10.2026 13:00</t>
+          <t>20.10.2026 14:00</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>588439</t>
+          <t>588450</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Закупка зимней одежды для управления главного механика.Обязательно предоставление сертификатов качества и обр…</t>
+          <t>Закупка зимней спецодежды для дворников-разнорабочих.Обязательно предоставление сертификатов качества и образ…</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -1540,7 +1547,7 @@
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="13" t="n"/>
       <c r="J21" s="10" t="n"/>
-      <c r="K21" s="15" t="inlineStr">
+      <c r="K21" s="16" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
@@ -1556,37 +1563,37 @@
         <v>19</v>
       </c>
       <c r="B22" s="10" t="n">
-        <v>159779</v>
+        <v>203056.8</v>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>20.10.2026 00:00</t>
+          <t>21.10.2026 13:00</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>ИМЗ-2026-010566</t>
+          <t>588439</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Поставка спецодежды</t>
+          <t>Закупка зимней одежды для управления главного механика.Обязательно предоставление сертификатов качества и обр…</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Бюджетное Профессиональное Образовательное учреждение Чуваш…</t>
+          <t>ООО «Карсар»</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Малые закупки · Малая закупка</t>
+          <t>Коммерческие · Конкурентный лист с переторжкой</t>
         </is>
       </c>
       <c r="H22" s="10" t="n"/>
       <c r="I22" s="13" t="n"/>
       <c r="J22" s="10" t="n"/>
-      <c r="K22" s="15" t="inlineStr">
+      <c r="K22" s="16" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
@@ -1602,37 +1609,37 @@
         <v>20</v>
       </c>
       <c r="B23" s="10" t="n">
-        <v>156229.45</v>
+        <v>159779</v>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>20.10.2026 06:00</t>
+          <t>20.10.2026 00:00</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>32616454697</t>
+          <t>ИМЗ-2026-010566</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Поставка спецодежды для нужд бюджетного учреждения Омской области «Комплексный центр социального обслуживания…</t>
+          <t>Поставка спецодежды</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>Бюджетное учреждение Омской обл. «Комплексный Центр Социаль…</t>
+          <t>Бюджетное Профессиональное Образовательное учреждение Чуваш…</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>223-ФЗ · Запрос котировок в электронной форме</t>
+          <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="13" t="n"/>
       <c r="J23" s="10" t="n"/>
-      <c r="K23" s="15" t="inlineStr">
+      <c r="K23" s="16" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
@@ -1648,44 +1655,44 @@
         <v>21</v>
       </c>
       <c r="B24" s="10" t="n">
-        <v>120000</v>
+        <v>156229.45</v>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>27.10.2026 09:00</t>
+          <t>20.10.2026 06:00</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>4067730</t>
+          <t>32616454697</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Запрос котировок в электронной форме № 31/ЗКТЭ-АО "РЖДстрой"/2026 на право заключения договора на поставку за…</t>
+          <t>Поставка спецодежды для нужд бюджетного учреждения Омской области «Комплексный центр социального обслуживания…</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>АО «Рждстрой»</t>
+          <t>Бюджетное учреждение Омской обл. «Комплексный Центр Социаль…</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос котировок</t>
+          <t>223-ФЗ · Запрос котировок в электронной форме</t>
         </is>
       </c>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="13" t="n"/>
       <c r="J24" s="10" t="n"/>
-      <c r="K24" s="15" t="inlineStr">
+      <c r="K24" s="16" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr">
         <is>
-          <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
@@ -1694,44 +1701,44 @@
         <v>22</v>
       </c>
       <c r="B25" s="10" t="n">
-        <v>119400</v>
+        <v>120000</v>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>21.10.2026 13:00</t>
+          <t>27.10.2026 09:00</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>10771691</t>
+          <t>4067730</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>поставка одежды для обучающихся из числа ОВЗ, проживающих в общежитии</t>
+          <t>Запрос котировок в электронной форме № 31/ЗКТЭ-АО "РЖДстрой"/2026 на право заключения договора на поставку за…</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Государственное бюджетное Профессиональное Образовательное …</t>
+          <t>АО «Рждстрой»</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Малые закупки · Малая закупка</t>
+          <t>Коммерческие · Запрос котировок</t>
         </is>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="13" t="n"/>
       <c r="J25" s="10" t="n"/>
-      <c r="K25" s="15" t="inlineStr">
+      <c r="K25" s="16" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
+          <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
         </is>
       </c>
     </row>
@@ -1740,26 +1747,26 @@
         <v>23</v>
       </c>
       <c r="B26" s="10" t="n">
-        <v>91010</v>
+        <v>119400</v>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>22.10.2026 15:17</t>
+          <t>21.10.2026 13:00</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>10763937</t>
+          <t>10771691</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Поставка мягкого инвентаря</t>
+          <t>поставка одежды для обучающихся из числа ОВЗ, проживающих в общежитии</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Государственное бюджетное Дошкольное Образовательное учрежд…</t>
+          <t>Государственное бюджетное Профессиональное Образовательное …</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -1770,7 +1777,7 @@
       <c r="H26" s="10" t="n"/>
       <c r="I26" s="13" t="n"/>
       <c r="J26" s="10" t="n"/>
-      <c r="K26" s="15" t="inlineStr">
+      <c r="K26" s="16" t="inlineStr">
         <is>
           <t>Посчитать: нужны позиции/цены</t>
         </is>
@@ -1782,48 +1789,48 @@
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="4" t="n">
+      <c r="A27" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>85614.06</v>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>22.10.2026 08:00</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>0128200000126006161</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>Закупка жилетов разгрузочных для государственного бюджетного учреждения здравоохранения Владимирской области …</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>ГБУЗ Владимирской обл. «Владимирская Областная Станция Скор…</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>44-ФЗ · Электронный аукцион</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>АУКЦИОН — не участвуем (справочно)</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>заявка: —; контракт: 10.00 %</t>
+      <c r="B27" s="10" t="n">
+        <v>91010</v>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>22.10.2026 15:17</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>10763937</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Поставка мягкого инвентаря</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>Государственное бюджетное Дошкольное Образовательное учрежд…</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>Малые закупки · Малая закупка</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="n"/>
+      <c r="I27" s="13" t="n"/>
+      <c r="J27" s="10" t="n"/>
+      <c r="K27" s="16" t="inlineStr">
+        <is>
+          <t>Посчитать: нужны позиции/цены</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
@@ -1832,26 +1839,26 @@
         <v>25</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>79800</v>
+        <v>85614.06</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 04:00</t>
+          <t>22.10.2026 08:00</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>0317300301926001566</t>
+          <t>0128200000126006161</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Поставка термобелья</t>
+          <t>Закупка жилетов разгрузочных для государственного бюджетного учреждения здравоохранения Владимирской области …</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>МКУ «Управление по делам гражданской обороны и чрезвычайным…</t>
+          <t>ГБУЗ Владимирской обл. «Владимирская Областная Станция Скор…</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -1869,7 +1876,7 @@
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>заявка: —; контракт: 30.00 %</t>
+          <t>заявка: —; контракт: 10.00 %</t>
         </is>
       </c>
     </row>
@@ -1878,26 +1885,26 @@
         <v>26</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>20495</v>
+        <v>79800</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>20.10.2026 06:00</t>
+          <t>28.10.2026 04:00</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>0260100000926000200</t>
+          <t>0317300301926001566</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Поставка респираторов медицинских FFP3</t>
+          <t>Поставка термобелья</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Федеральное бюджетное учреждение Центр Реабилитации Фонда П…</t>
+          <t>МКУ «Управление по делам гражданской обороны и чрезвычайным…</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -1915,53 +1922,53 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
+          <t>заявка: —; контракт: 30.00 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>20495</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>20.10.2026 06:00</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>0260100000926000200</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Поставка респираторов медицинских FFP3</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Федеральное бюджетное учреждение Центр Реабилитации Фонда П…</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>44-ФЗ · Электронный аукцион</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>АУКЦИОН — не участвуем (справочно)</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
           <t>заявка: —; контракт: 10.00 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" s="10" t="n">
-        <v>12908</v>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>21.10.2026 14:12</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>BP01597186</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>Приобретение средств индивидуальной защиты</t>
-        </is>
-      </c>
-      <c r="F30" s="12" t="inlineStr">
-        <is>
-          <t>МБУДО «Детская Школа Искусств Имени А.И.Островского» Городс…</t>
-        </is>
-      </c>
-      <c r="G30" s="12" t="inlineStr">
-        <is>
-          <t>Малые закупки · Малая закупка</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="n"/>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="10" t="n"/>
-      <c r="K30" s="15" t="inlineStr">
-        <is>
-          <t>Посчитать: нужны позиции/цены</t>
-        </is>
-      </c>
-      <c r="L30" s="12" t="inlineStr">
-        <is>
-          <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
@@ -1969,38 +1976,40 @@
       <c r="A31" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="10" t="n"/>
+      <c r="B31" s="10" t="n">
+        <v>12908</v>
+      </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>20.10.2026 10:00</t>
+          <t>21.10.2026 14:12</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>4640791</t>
+          <t>BP01597186</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>RUNEV-11855, Аварийно-спасательное снаряжение - АО "Невинномысский Азот" - Ставропольский край</t>
+          <t>Приобретение средств индивидуальной защиты</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>ОАО «Невинномысский Азот»</t>
+          <t>МБУДО «Детская Школа Искусств Имени А.И.Островского» Городс…</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос предложений</t>
+          <t>Малые закупки · Малая закупка</t>
         </is>
       </c>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="13" t="n"/>
       <c r="J31" s="10" t="n"/>
-      <c r="K31" s="23" t="inlineStr">
-        <is>
-          <t>КП — запросить спецификацию</t>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>Посчитать: нужны позиции/цены</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
@@ -2016,22 +2025,22 @@
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>20.10.2026 15:00</t>
+          <t>20.10.2026 10:00</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>4638478</t>
+          <t>4640791</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>закупка спецодежды, СИЗ (поставка ноябрь 2026 - январь 2027 ежемесячно) для нужд ГК "УралМетКом" (ООО "УралМе…</t>
+          <t>RUNEV-11855, Аварийно-спасательное снаряжение - АО "Невинномысский Азот" - Ставропольский край</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>ООО «Уралметком»</t>
+          <t>ОАО «Невинномысский Азот»</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
@@ -2042,7 +2051,7 @@
       <c r="H32" s="10" t="n"/>
       <c r="I32" s="13" t="n"/>
       <c r="J32" s="10" t="n"/>
-      <c r="K32" s="23" t="inlineStr">
+      <c r="K32" s="24" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
@@ -2060,33 +2069,33 @@
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>20.10.2026 12:00</t>
+          <t>20.10.2026 15:00</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>385-495</t>
+          <t>4638478</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Спецодежда для персонала клининга и технической службы ГК Мэдокс</t>
+          <t>закупка спецодежды, СИЗ (поставка ноябрь 2026 - январь 2027 ежемесячно) для нужд ГК "УралМетКом" (ООО "УралМе…</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>ООО «Мэдокс»</t>
+          <t>ООО «Уралметком»</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>Коммерческие · Запрос предложений</t>
         </is>
       </c>
       <c r="H33" s="10" t="n"/>
       <c r="I33" s="13" t="n"/>
       <c r="J33" s="10" t="n"/>
-      <c r="K33" s="23" t="inlineStr">
+      <c r="K33" s="24" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
@@ -2104,35 +2113,35 @@
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>21.10.2026 23:59</t>
+          <t>20.10.2026 12:00</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>3506604</t>
+          <t>385-495</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Поставка спецодежды и спецобуви для нужд Базы АО «В/О «Изотоп»</t>
+          <t>Спецодежда для персонала клининга и технической службы ГК Мэдокс</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>АО «Всерегиональное Объединение «Изотоп»</t>
+          <t>ООО «Мэдокс»</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>Коммерческие · Мониторинг цен</t>
+          <t>Коммерческие · Тендер</t>
         </is>
       </c>
       <c r="H34" s="10" t="n"/>
       <c r="I34" s="13" t="n"/>
       <c r="J34" s="10" t="n"/>
-      <c r="K34" s="23" t="inlineStr">
-        <is>
-          <t>КП (сбор цен, без обязательств)</t>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>КП — запросить спецификацию</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr">
@@ -2148,35 +2157,35 @@
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>21.10.2026 17:00</t>
+          <t>21.10.2026 23:59</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>4638381</t>
+          <t>3506604</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>«Бронежилеты и бронеодежда_КЧХК_10.2026»</t>
+          <t>Поставка спецодежды и спецобуви для нужд Базы АО «В/О «Изотоп»</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>Кчхк АО Охк Уралхим в г. К-Чепецке, ФЛ</t>
+          <t>АО «Всерегиональное Объединение «Изотоп»</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Коммерческие · Процедура закупки</t>
+          <t>Коммерческие · Мониторинг цен</t>
         </is>
       </c>
       <c r="H35" s="10" t="n"/>
       <c r="I35" s="13" t="n"/>
       <c r="J35" s="10" t="n"/>
-      <c r="K35" s="23" t="inlineStr">
-        <is>
-          <t>КП — запросить спецификацию</t>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>КП (сбор цен, без обязательств)</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
@@ -2192,33 +2201,33 @@
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>21.10.2026 09:00</t>
+          <t>21.10.2026 17:00</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>384-590</t>
+          <t>4638381</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Закупка средств индивидуальной защиты (СИЗ рук, глаз), влагозащитной одежды и нательного белья</t>
+          <t>«Бронежилеты и бронеодежда_КЧХК_10.2026»</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>ООО «Аэрозоль Новомосковск»</t>
+          <t>Кчхк АО Охк Уралхим в г. К-Чепецке, ФЛ</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>Коммерческие · Процедура закупки</t>
         </is>
       </c>
       <c r="H36" s="10" t="n"/>
       <c r="I36" s="13" t="n"/>
       <c r="J36" s="10" t="n"/>
-      <c r="K36" s="23" t="inlineStr">
+      <c r="K36" s="24" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
@@ -2236,33 +2245,33 @@
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>21.10.2026 16:54</t>
+          <t>21.10.2026 09:00</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>4642906</t>
+          <t>384-590</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Спецодежда, обувь и СИЗ</t>
+          <t>Закупка средств индивидуальной защиты (СИЗ рук, глаз), влагозащитной одежды и нательного белья</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>ООО «Калинов Мост»</t>
+          <t>ООО «Аэрозоль Новомосковск»</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос предложений</t>
+          <t>Коммерческие · Тендер</t>
         </is>
       </c>
       <c r="H37" s="10" t="n"/>
       <c r="I37" s="13" t="n"/>
       <c r="J37" s="10" t="n"/>
-      <c r="K37" s="23" t="inlineStr">
+      <c r="K37" s="24" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
@@ -2280,35 +2289,35 @@
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>21.10.2026 07:07</t>
+          <t>21.10.2026 16:54</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>0573400000126006237</t>
+          <t>4642906</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Поставка специальной одежды, специальной обуви и других средств индивидуальной защиты для нужд Владивостокско…</t>
+          <t>Спецодежда, обувь и СИЗ</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>ФГУП «Государственная Корпорация по Организации Воздушного …</t>
+          <t>ООО «Калинов Мост»</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>44-ФЗ · Запрос цен</t>
+          <t>Коммерческие · Запрос предложений</t>
         </is>
       </c>
       <c r="H38" s="10" t="n"/>
       <c r="I38" s="13" t="n"/>
       <c r="J38" s="10" t="n"/>
-      <c r="K38" s="23" t="inlineStr">
-        <is>
-          <t>КП (сбор цен, без обязательств)</t>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>КП — запросить спецификацию</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
@@ -2324,35 +2333,35 @@
       <c r="B39" s="10" t="n"/>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>22.10.2026 11:00</t>
+          <t>21.10.2026 07:07</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>311-335</t>
+          <t>0573400000126006237</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Закупка_ Консолидированная закупка СИЗ 2027 г._ просьба подать ваше предложение+ подготовить невозвратные обр…</t>
+          <t>Поставка специальной одежды, специальной обуви и других средств индивидуальной защиты для нужд Владивостокско…</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>АО «Прогресс»</t>
+          <t>ФГУП «Государственная Корпорация по Организации Воздушного …</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>44-ФЗ · Запрос цен</t>
         </is>
       </c>
       <c r="H39" s="10" t="n"/>
       <c r="I39" s="13" t="n"/>
       <c r="J39" s="10" t="n"/>
-      <c r="K39" s="23" t="inlineStr">
-        <is>
-          <t>КП — запросить спецификацию</t>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>КП (сбор цен, без обязательств)</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
@@ -2368,35 +2377,35 @@
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>23.10.2026 12:00</t>
+          <t>22.10.2026 11:00</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>4644624</t>
+          <t>311-335</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Респиратор фильтрующий Респираторный комплекс Алина-316 FFP3 R D ПДК50</t>
+          <t>Закупка_ Консолидированная закупка СИЗ 2027 г._ просьба подать ваше предложение+ подготовить невозвратные обр…</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>ООО УК «Пмх»</t>
+          <t>АО «Прогресс»</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>Коммерческие · Запрос цен</t>
+          <t>Коммерческие · Тендер</t>
         </is>
       </c>
       <c r="H40" s="10" t="n"/>
       <c r="I40" s="13" t="n"/>
       <c r="J40" s="10" t="n"/>
-      <c r="K40" s="23" t="inlineStr">
-        <is>
-          <t>КП (сбор цен, без обязательств)</t>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>КП — запросить спецификацию</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
@@ -2412,35 +2421,35 @@
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>23.10.2026 11:00</t>
+          <t>23.10.2026 12:00</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>381-629</t>
+          <t>4644624</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Закупка зимней спецодежды для ООО "Заречное". 2026г.</t>
+          <t>Респиратор фильтрующий Респираторный комплекс Алина-316 FFP3 R D ПДК50</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>АО «Агрохолдинг «Просторы»</t>
+          <t>ООО УК «Пмх»</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>Коммерческие · Тендер</t>
+          <t>Коммерческие · Запрос цен</t>
         </is>
       </c>
       <c r="H41" s="10" t="n"/>
       <c r="I41" s="13" t="n"/>
       <c r="J41" s="10" t="n"/>
-      <c r="K41" s="23" t="inlineStr">
-        <is>
-          <t>КП — запросить спецификацию</t>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>КП (сбор цен, без обязательств)</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
@@ -2456,22 +2465,22 @@
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>23.10.2026 14:00</t>
+          <t>23.10.2026 11:00</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>385-418</t>
+          <t>381-629</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Закупка СИЗ г. Набережные Челны</t>
+          <t>Закупка зимней спецодежды для ООО "Заречное". 2026г.</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>ООО «Агк»</t>
+          <t>АО «Агрохолдинг «Просторы»</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
@@ -2482,7 +2491,7 @@
       <c r="H42" s="10" t="n"/>
       <c r="I42" s="13" t="n"/>
       <c r="J42" s="10" t="n"/>
-      <c r="K42" s="23" t="inlineStr">
+      <c r="K42" s="24" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
@@ -2500,22 +2509,22 @@
       <c r="B43" s="10" t="n"/>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>26.10.2026 17:40</t>
+          <t>23.10.2026 14:00</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>386-076</t>
+          <t>385-418</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Ботинки с высокими берцами - 4 000 пар</t>
+          <t>Закупка СИЗ г. Набережные Челны</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>ООО «Союзспецодежда»</t>
+          <t>ООО «Агк»</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -2526,14 +2535,14 @@
       <c r="H43" s="10" t="n"/>
       <c r="I43" s="13" t="n"/>
       <c r="J43" s="10" t="n"/>
-      <c r="K43" s="23" t="inlineStr">
+      <c r="K43" s="24" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>заявка: не указано (обычно нет); контракт: не указано; аванс: не указан — запросить; оплата: запросить (обычно 30–90 дн.)</t>
+          <t>заявка: —; контракт: —; аванс: не указан</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2579,7 @@
       <c r="H44" s="10" t="n"/>
       <c r="I44" s="13" t="n"/>
       <c r="J44" s="10" t="n"/>
-      <c r="K44" s="23" t="inlineStr">
+      <c r="K44" s="24" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
@@ -2616,7 +2625,7 @@
       </c>
       <c r="I45" s="13" t="n"/>
       <c r="J45" s="10" t="n"/>
-      <c r="K45" s="23" t="inlineStr">
+      <c r="K45" s="24" t="inlineStr">
         <is>
           <t>КП ≈ 1 612 597 ₽ (без НМЦК)</t>
         </is>
@@ -2660,7 +2669,7 @@
       <c r="H46" s="10" t="n"/>
       <c r="I46" s="13" t="n"/>
       <c r="J46" s="10" t="n"/>
-      <c r="K46" s="23" t="inlineStr">
+      <c r="K46" s="24" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
@@ -2704,7 +2713,7 @@
       <c r="H47" s="10" t="n"/>
       <c r="I47" s="13" t="n"/>
       <c r="J47" s="10" t="n"/>
-      <c r="K47" s="23" t="inlineStr">
+      <c r="K47" s="24" t="inlineStr">
         <is>
           <t>КП — запросить спецификацию</t>
         </is>
@@ -2716,24 +2725,24 @@
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
-      <c r="A48" s="24" t="inlineStr"/>
-      <c r="B48" s="25" t="n">
+      <c r="A48" s="25" t="inlineStr"/>
+      <c r="B48" s="26" t="n">
         <v>217686522.34</v>
       </c>
-      <c r="C48" s="24" t="inlineStr"/>
-      <c r="D48" s="24" t="inlineStr"/>
-      <c r="E48" s="24" t="inlineStr">
+      <c r="C48" s="25" t="inlineStr"/>
+      <c r="D48" s="25" t="inlineStr"/>
+      <c r="E48" s="25" t="inlineStr">
         <is>
           <t>ИТОГО НМЦК без аукционов</t>
         </is>
       </c>
-      <c r="F48" s="26" t="n"/>
-      <c r="G48" s="26" t="n"/>
-      <c r="H48" s="26" t="n"/>
-      <c r="I48" s="26" t="n"/>
-      <c r="J48" s="26" t="n"/>
-      <c r="K48" s="26" t="n"/>
-      <c r="L48" s="26" t="n"/>
+      <c r="F48" s="27" t="n"/>
+      <c r="G48" s="27" t="n"/>
+      <c r="H48" s="27" t="n"/>
+      <c r="I48" s="27" t="n"/>
+      <c r="J48" s="27" t="n"/>
+      <c r="K48" s="27" t="n"/>
+      <c r="L48" s="27" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:L47"/>
